--- a/master_parts.xlsx
+++ b/master_parts.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WIPHAPHON-PCRY\Desktop\Test AI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40F7E479-63E7-496F-B48E-0EEEF7926CFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44ED942E-9811-43EC-9896-03DC733DB9AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="2520" windowWidth="24240" windowHeight="13020" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Pressure &amp; Leakage Test" sheetId="4" state="hidden" r:id="rId1"/>
@@ -2050,269 +2050,269 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="34" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="35" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="21" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="25" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="26" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="33" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="38" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="39" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="36" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="22" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="36" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="38" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="38" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="63" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="22" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="60" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="61" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="62" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="49" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="44" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="45" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="47" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="34" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="35" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="21" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="25" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="26" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="38" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="33" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="39" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="38" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="38" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="60" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="61" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="62" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="49" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="44" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="45" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="47" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="63" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4348,29 +4348,29 @@
       <c r="K1" s="4"/>
       <c r="L1" s="4"/>
       <c r="M1" s="4"/>
-      <c r="N1" s="104" t="s">
+      <c r="N1" s="90" t="s">
         <v>42</v>
       </c>
-      <c r="O1" s="105"/>
-      <c r="P1" s="105"/>
-      <c r="Q1" s="105"/>
-      <c r="R1" s="105"/>
-      <c r="S1" s="105"/>
-      <c r="T1" s="105"/>
-      <c r="U1" s="105"/>
-      <c r="V1" s="105"/>
-      <c r="W1" s="105"/>
-      <c r="X1" s="105"/>
-      <c r="Y1" s="105"/>
-      <c r="Z1" s="105"/>
-      <c r="AA1" s="105"/>
-      <c r="AB1" s="105"/>
-      <c r="AC1" s="105"/>
-      <c r="AD1" s="105"/>
-      <c r="AE1" s="105"/>
-      <c r="AF1" s="105"/>
-      <c r="AG1" s="105"/>
-      <c r="AH1" s="106"/>
+      <c r="O1" s="91"/>
+      <c r="P1" s="91"/>
+      <c r="Q1" s="91"/>
+      <c r="R1" s="91"/>
+      <c r="S1" s="91"/>
+      <c r="T1" s="91"/>
+      <c r="U1" s="91"/>
+      <c r="V1" s="91"/>
+      <c r="W1" s="91"/>
+      <c r="X1" s="91"/>
+      <c r="Y1" s="91"/>
+      <c r="Z1" s="91"/>
+      <c r="AA1" s="91"/>
+      <c r="AB1" s="91"/>
+      <c r="AC1" s="91"/>
+      <c r="AD1" s="91"/>
+      <c r="AE1" s="91"/>
+      <c r="AF1" s="91"/>
+      <c r="AG1" s="91"/>
+      <c r="AH1" s="92"/>
       <c r="AI1" s="77" t="s">
         <v>0</v>
       </c>
@@ -4380,15 +4380,15 @@
       <c r="AM1" s="75"/>
       <c r="AN1" s="75"/>
       <c r="AO1" s="76"/>
-      <c r="AP1" s="97"/>
-      <c r="AQ1" s="98"/>
-      <c r="AR1" s="98"/>
-      <c r="AS1" s="98"/>
-      <c r="AT1" s="98"/>
-      <c r="AU1" s="98"/>
-      <c r="AV1" s="98"/>
-      <c r="AW1" s="98"/>
-      <c r="AX1" s="99"/>
+      <c r="AP1" s="99"/>
+      <c r="AQ1" s="100"/>
+      <c r="AR1" s="100"/>
+      <c r="AS1" s="100"/>
+      <c r="AT1" s="100"/>
+      <c r="AU1" s="100"/>
+      <c r="AV1" s="100"/>
+      <c r="AW1" s="100"/>
+      <c r="AX1" s="101"/>
     </row>
     <row r="2" spans="1:50" s="6" customFormat="1" ht="24.95" customHeight="1">
       <c r="A2" s="7"/>
@@ -4404,27 +4404,27 @@
       <c r="K2" s="61"/>
       <c r="L2" s="44"/>
       <c r="M2" s="44"/>
-      <c r="N2" s="107"/>
-      <c r="O2" s="108"/>
-      <c r="P2" s="108"/>
-      <c r="Q2" s="108"/>
-      <c r="R2" s="108"/>
-      <c r="S2" s="108"/>
-      <c r="T2" s="108"/>
-      <c r="U2" s="108"/>
-      <c r="V2" s="108"/>
-      <c r="W2" s="108"/>
-      <c r="X2" s="108"/>
-      <c r="Y2" s="108"/>
-      <c r="Z2" s="108"/>
-      <c r="AA2" s="108"/>
-      <c r="AB2" s="108"/>
-      <c r="AC2" s="108"/>
-      <c r="AD2" s="108"/>
-      <c r="AE2" s="108"/>
-      <c r="AF2" s="108"/>
-      <c r="AG2" s="108"/>
-      <c r="AH2" s="109"/>
+      <c r="N2" s="93"/>
+      <c r="O2" s="94"/>
+      <c r="P2" s="94"/>
+      <c r="Q2" s="94"/>
+      <c r="R2" s="94"/>
+      <c r="S2" s="94"/>
+      <c r="T2" s="94"/>
+      <c r="U2" s="94"/>
+      <c r="V2" s="94"/>
+      <c r="W2" s="94"/>
+      <c r="X2" s="94"/>
+      <c r="Y2" s="94"/>
+      <c r="Z2" s="94"/>
+      <c r="AA2" s="94"/>
+      <c r="AB2" s="94"/>
+      <c r="AC2" s="94"/>
+      <c r="AD2" s="94"/>
+      <c r="AE2" s="94"/>
+      <c r="AF2" s="94"/>
+      <c r="AG2" s="94"/>
+      <c r="AH2" s="95"/>
       <c r="AI2" s="74" t="s">
         <v>1</v>
       </c>
@@ -4434,15 +4434,15 @@
       <c r="AM2" s="68"/>
       <c r="AN2" s="69"/>
       <c r="AO2" s="70"/>
-      <c r="AP2" s="100"/>
-      <c r="AQ2" s="101"/>
-      <c r="AR2" s="101"/>
-      <c r="AS2" s="101"/>
-      <c r="AT2" s="101"/>
-      <c r="AU2" s="101"/>
-      <c r="AV2" s="101"/>
-      <c r="AW2" s="101"/>
-      <c r="AX2" s="102"/>
+      <c r="AP2" s="102"/>
+      <c r="AQ2" s="103"/>
+      <c r="AR2" s="103"/>
+      <c r="AS2" s="103"/>
+      <c r="AT2" s="103"/>
+      <c r="AU2" s="103"/>
+      <c r="AV2" s="103"/>
+      <c r="AW2" s="103"/>
+      <c r="AX2" s="104"/>
     </row>
     <row r="3" spans="1:50" s="6" customFormat="1" ht="24.95" customHeight="1">
       <c r="A3" s="9"/>
@@ -4458,27 +4458,27 @@
       <c r="K3" s="13"/>
       <c r="L3" s="14"/>
       <c r="M3" s="14"/>
-      <c r="N3" s="110"/>
-      <c r="O3" s="111"/>
-      <c r="P3" s="111"/>
-      <c r="Q3" s="111"/>
-      <c r="R3" s="111"/>
-      <c r="S3" s="111"/>
-      <c r="T3" s="111"/>
-      <c r="U3" s="111"/>
-      <c r="V3" s="111"/>
-      <c r="W3" s="111"/>
-      <c r="X3" s="111"/>
-      <c r="Y3" s="111"/>
-      <c r="Z3" s="111"/>
-      <c r="AA3" s="111"/>
-      <c r="AB3" s="111"/>
-      <c r="AC3" s="111"/>
-      <c r="AD3" s="111"/>
-      <c r="AE3" s="111"/>
-      <c r="AF3" s="111"/>
-      <c r="AG3" s="111"/>
-      <c r="AH3" s="112"/>
+      <c r="N3" s="96"/>
+      <c r="O3" s="97"/>
+      <c r="P3" s="97"/>
+      <c r="Q3" s="97"/>
+      <c r="R3" s="97"/>
+      <c r="S3" s="97"/>
+      <c r="T3" s="97"/>
+      <c r="U3" s="97"/>
+      <c r="V3" s="97"/>
+      <c r="W3" s="97"/>
+      <c r="X3" s="97"/>
+      <c r="Y3" s="97"/>
+      <c r="Z3" s="97"/>
+      <c r="AA3" s="97"/>
+      <c r="AB3" s="97"/>
+      <c r="AC3" s="97"/>
+      <c r="AD3" s="97"/>
+      <c r="AE3" s="97"/>
+      <c r="AF3" s="97"/>
+      <c r="AG3" s="97"/>
+      <c r="AH3" s="98"/>
       <c r="AI3" s="74" t="s">
         <v>2</v>
       </c>
@@ -4488,15 +4488,15 @@
       <c r="AM3" s="67"/>
       <c r="AN3" s="67"/>
       <c r="AO3" s="73"/>
-      <c r="AP3" s="116"/>
-      <c r="AQ3" s="117"/>
-      <c r="AR3" s="117"/>
-      <c r="AS3" s="117"/>
-      <c r="AT3" s="117"/>
-      <c r="AU3" s="117"/>
-      <c r="AV3" s="117"/>
-      <c r="AW3" s="117"/>
-      <c r="AX3" s="118"/>
+      <c r="AP3" s="105"/>
+      <c r="AQ3" s="106"/>
+      <c r="AR3" s="106"/>
+      <c r="AS3" s="106"/>
+      <c r="AT3" s="106"/>
+      <c r="AU3" s="106"/>
+      <c r="AV3" s="106"/>
+      <c r="AW3" s="106"/>
+      <c r="AX3" s="107"/>
     </row>
     <row r="4" spans="1:50" ht="20.100000000000001" customHeight="1">
       <c r="A4" s="15"/>
@@ -4624,36 +4624,36 @@
       <c r="S6" s="35"/>
       <c r="T6"/>
       <c r="U6"/>
-      <c r="V6" s="113" t="s">
+      <c r="V6" s="110" t="s">
         <v>27</v>
       </c>
-      <c r="W6" s="114"/>
-      <c r="X6" s="114"/>
-      <c r="Y6" s="114"/>
-      <c r="Z6" s="114"/>
-      <c r="AA6" s="114"/>
-      <c r="AB6" s="114"/>
-      <c r="AC6" s="114"/>
-      <c r="AD6" s="114"/>
-      <c r="AE6" s="114"/>
-      <c r="AF6" s="114"/>
-      <c r="AG6" s="114"/>
-      <c r="AH6" s="114"/>
-      <c r="AI6" s="114"/>
-      <c r="AJ6" s="114"/>
-      <c r="AK6" s="114"/>
-      <c r="AL6" s="114"/>
-      <c r="AM6" s="114"/>
-      <c r="AN6" s="114"/>
-      <c r="AO6" s="114"/>
-      <c r="AP6" s="114"/>
-      <c r="AQ6" s="114"/>
-      <c r="AR6" s="114"/>
-      <c r="AS6" s="114"/>
-      <c r="AT6" s="114"/>
-      <c r="AU6" s="114"/>
-      <c r="AV6" s="114"/>
-      <c r="AW6" s="119"/>
+      <c r="W6" s="111"/>
+      <c r="X6" s="111"/>
+      <c r="Y6" s="111"/>
+      <c r="Z6" s="111"/>
+      <c r="AA6" s="111"/>
+      <c r="AB6" s="111"/>
+      <c r="AC6" s="111"/>
+      <c r="AD6" s="111"/>
+      <c r="AE6" s="111"/>
+      <c r="AF6" s="111"/>
+      <c r="AG6" s="111"/>
+      <c r="AH6" s="111"/>
+      <c r="AI6" s="111"/>
+      <c r="AJ6" s="111"/>
+      <c r="AK6" s="111"/>
+      <c r="AL6" s="111"/>
+      <c r="AM6" s="111"/>
+      <c r="AN6" s="111"/>
+      <c r="AO6" s="111"/>
+      <c r="AP6" s="111"/>
+      <c r="AQ6" s="111"/>
+      <c r="AR6" s="111"/>
+      <c r="AS6" s="111"/>
+      <c r="AT6" s="111"/>
+      <c r="AU6" s="111"/>
+      <c r="AV6" s="111"/>
+      <c r="AW6" s="112"/>
       <c r="AX6" s="18"/>
     </row>
     <row r="7" spans="1:50" s="6" customFormat="1" ht="20.100000000000001" customHeight="1">
@@ -4669,54 +4669,54 @@
       <c r="H7" s="30">
         <v>1</v>
       </c>
-      <c r="I7" s="90" t="e">
+      <c r="I7" s="89" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="J7" s="90"/>
-      <c r="K7" s="90"/>
-      <c r="L7" s="90"/>
-      <c r="M7" s="90"/>
-      <c r="N7" s="90"/>
-      <c r="O7" s="90"/>
-      <c r="P7" s="90"/>
-      <c r="Q7" s="90"/>
+      <c r="J7" s="89"/>
+      <c r="K7" s="89"/>
+      <c r="L7" s="89"/>
+      <c r="M7" s="89"/>
+      <c r="N7" s="89"/>
+      <c r="O7" s="89"/>
+      <c r="P7" s="89"/>
+      <c r="Q7" s="89"/>
       <c r="R7" s="35"/>
       <c r="S7" s="35"/>
       <c r="T7"/>
       <c r="U7"/>
       <c r="V7" s="36"/>
-      <c r="W7" s="89" t="s">
+      <c r="W7" s="108" t="s">
         <v>3</v>
       </c>
-      <c r="X7" s="89"/>
-      <c r="Y7" s="89"/>
-      <c r="Z7" s="89"/>
-      <c r="AA7" s="89"/>
-      <c r="AB7" s="115" t="e">
+      <c r="X7" s="108"/>
+      <c r="Y7" s="108"/>
+      <c r="Z7" s="108"/>
+      <c r="AA7" s="108"/>
+      <c r="AB7" s="109" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="AC7" s="115"/>
-      <c r="AD7" s="115"/>
-      <c r="AE7" s="115"/>
-      <c r="AF7" s="115"/>
-      <c r="AG7" s="115"/>
-      <c r="AH7" s="115"/>
-      <c r="AI7" s="115"/>
-      <c r="AJ7" s="115"/>
-      <c r="AK7" s="115"/>
-      <c r="AL7" s="115"/>
-      <c r="AM7" s="115"/>
-      <c r="AN7" s="115"/>
-      <c r="AO7" s="115"/>
-      <c r="AP7" s="115"/>
-      <c r="AQ7" s="115"/>
-      <c r="AR7" s="115"/>
-      <c r="AS7" s="115"/>
-      <c r="AT7" s="115"/>
-      <c r="AU7" s="115"/>
-      <c r="AV7" s="115"/>
+      <c r="AC7" s="109"/>
+      <c r="AD7" s="109"/>
+      <c r="AE7" s="109"/>
+      <c r="AF7" s="109"/>
+      <c r="AG7" s="109"/>
+      <c r="AH7" s="109"/>
+      <c r="AI7" s="109"/>
+      <c r="AJ7" s="109"/>
+      <c r="AK7" s="109"/>
+      <c r="AL7" s="109"/>
+      <c r="AM7" s="109"/>
+      <c r="AN7" s="109"/>
+      <c r="AO7" s="109"/>
+      <c r="AP7" s="109"/>
+      <c r="AQ7" s="109"/>
+      <c r="AR7" s="109"/>
+      <c r="AS7" s="109"/>
+      <c r="AT7" s="109"/>
+      <c r="AU7" s="109"/>
+      <c r="AV7" s="109"/>
       <c r="AW7" s="39"/>
       <c r="AX7" s="18"/>
     </row>
@@ -4731,18 +4731,18 @@
       <c r="H8" s="30">
         <v>2</v>
       </c>
-      <c r="I8" s="90" t="e">
+      <c r="I8" s="89" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="J8" s="90"/>
-      <c r="K8" s="90"/>
-      <c r="L8" s="90"/>
-      <c r="M8" s="90"/>
-      <c r="N8" s="90"/>
-      <c r="O8" s="90"/>
-      <c r="P8" s="90"/>
-      <c r="Q8" s="90"/>
+      <c r="J8" s="89"/>
+      <c r="K8" s="89"/>
+      <c r="L8" s="89"/>
+      <c r="M8" s="89"/>
+      <c r="N8" s="89"/>
+      <c r="O8" s="89"/>
+      <c r="P8" s="89"/>
+      <c r="Q8" s="89"/>
       <c r="R8" s="30">
         <v>2</v>
       </c>
@@ -4759,29 +4759,29 @@
       <c r="Y8" s="37"/>
       <c r="Z8" s="37"/>
       <c r="AA8" s="32"/>
-      <c r="AB8" s="90" t="s">
+      <c r="AB8" s="89" t="s">
         <v>43</v>
       </c>
-      <c r="AC8" s="90"/>
-      <c r="AD8" s="90"/>
-      <c r="AE8" s="90"/>
-      <c r="AF8" s="90"/>
-      <c r="AG8" s="90"/>
-      <c r="AH8" s="90"/>
-      <c r="AI8" s="90"/>
-      <c r="AJ8" s="90"/>
-      <c r="AK8" s="90"/>
-      <c r="AL8" s="90"/>
-      <c r="AM8" s="90"/>
-      <c r="AN8" s="90"/>
-      <c r="AO8" s="90"/>
-      <c r="AP8" s="90"/>
-      <c r="AQ8" s="90"/>
-      <c r="AR8" s="90"/>
-      <c r="AS8" s="90"/>
-      <c r="AT8" s="90"/>
-      <c r="AU8" s="90"/>
-      <c r="AV8" s="90"/>
+      <c r="AC8" s="89"/>
+      <c r="AD8" s="89"/>
+      <c r="AE8" s="89"/>
+      <c r="AF8" s="89"/>
+      <c r="AG8" s="89"/>
+      <c r="AH8" s="89"/>
+      <c r="AI8" s="89"/>
+      <c r="AJ8" s="89"/>
+      <c r="AK8" s="89"/>
+      <c r="AL8" s="89"/>
+      <c r="AM8" s="89"/>
+      <c r="AN8" s="89"/>
+      <c r="AO8" s="89"/>
+      <c r="AP8" s="89"/>
+      <c r="AQ8" s="89"/>
+      <c r="AR8" s="89"/>
+      <c r="AS8" s="89"/>
+      <c r="AT8" s="89"/>
+      <c r="AU8" s="89"/>
+      <c r="AV8" s="89"/>
       <c r="AW8" s="39"/>
       <c r="AX8" s="18"/>
     </row>
@@ -4796,18 +4796,18 @@
       <c r="H9" s="30">
         <v>3</v>
       </c>
-      <c r="I9" s="90" t="e">
+      <c r="I9" s="89" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="J9" s="90"/>
-      <c r="K9" s="90"/>
-      <c r="L9" s="90"/>
-      <c r="M9" s="90"/>
-      <c r="N9" s="90"/>
-      <c r="O9" s="90"/>
-      <c r="P9" s="90"/>
-      <c r="Q9" s="90"/>
+      <c r="J9" s="89"/>
+      <c r="K9" s="89"/>
+      <c r="L9" s="89"/>
+      <c r="M9" s="89"/>
+      <c r="N9" s="89"/>
+      <c r="O9" s="89"/>
+      <c r="P9" s="89"/>
+      <c r="Q9" s="89"/>
       <c r="R9">
         <v>1</v>
       </c>
@@ -4817,31 +4817,31 @@
       <c r="T9"/>
       <c r="U9"/>
       <c r="V9" s="36"/>
-      <c r="W9" s="89" t="s">
+      <c r="W9" s="108" t="s">
         <v>30</v>
       </c>
-      <c r="X9" s="89"/>
-      <c r="Y9" s="89"/>
-      <c r="Z9" s="89"/>
-      <c r="AA9" s="90">
+      <c r="X9" s="108"/>
+      <c r="Y9" s="108"/>
+      <c r="Z9" s="108"/>
+      <c r="AA9" s="89">
         <v>18</v>
       </c>
-      <c r="AB9" s="90"/>
+      <c r="AB9" s="89"/>
       <c r="AC9" s="57" t="s">
         <v>26</v>
       </c>
-      <c r="AD9" s="90">
+      <c r="AD9" s="89">
         <v>10</v>
       </c>
-      <c r="AE9" s="90"/>
+      <c r="AE9" s="89"/>
       <c r="AF9" s="57" t="s">
         <v>26</v>
       </c>
-      <c r="AG9" s="90">
+      <c r="AG9" s="89">
         <v>2018</v>
       </c>
-      <c r="AH9" s="90"/>
-      <c r="AI9" s="90"/>
+      <c r="AH9" s="89"/>
+      <c r="AI9" s="89"/>
       <c r="AJ9"/>
       <c r="AK9"/>
       <c r="AL9"/>
@@ -4869,18 +4869,18 @@
       <c r="H10" s="30">
         <v>4</v>
       </c>
-      <c r="I10" s="90" t="e">
+      <c r="I10" s="89" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="J10" s="90"/>
-      <c r="K10" s="90"/>
-      <c r="L10" s="90"/>
-      <c r="M10" s="90"/>
-      <c r="N10" s="90"/>
-      <c r="O10" s="90"/>
-      <c r="P10" s="90"/>
-      <c r="Q10" s="90"/>
+      <c r="J10" s="89"/>
+      <c r="K10" s="89"/>
+      <c r="L10" s="89"/>
+      <c r="M10" s="89"/>
+      <c r="N10" s="89"/>
+      <c r="O10" s="89"/>
+      <c r="P10" s="89"/>
+      <c r="Q10" s="89"/>
       <c r="R10">
         <v>1</v>
       </c>
@@ -4890,37 +4890,37 @@
       <c r="T10"/>
       <c r="U10"/>
       <c r="V10" s="36"/>
-      <c r="W10" s="89" t="s">
+      <c r="W10" s="108" t="s">
         <v>15</v>
       </c>
-      <c r="X10" s="89"/>
-      <c r="Y10" s="89"/>
-      <c r="Z10" s="89"/>
-      <c r="AA10" s="89"/>
-      <c r="AB10" s="90" t="e">
+      <c r="X10" s="108"/>
+      <c r="Y10" s="108"/>
+      <c r="Z10" s="108"/>
+      <c r="AA10" s="108"/>
+      <c r="AB10" s="89" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="AC10" s="90"/>
-      <c r="AD10" s="90"/>
-      <c r="AE10" s="90"/>
-      <c r="AF10" s="90"/>
-      <c r="AG10" s="90"/>
-      <c r="AH10" s="90"/>
-      <c r="AI10" s="90"/>
-      <c r="AJ10" s="90"/>
-      <c r="AK10" s="90"/>
-      <c r="AL10" s="90"/>
-      <c r="AM10" s="90"/>
-      <c r="AN10" s="90"/>
-      <c r="AO10" s="90"/>
-      <c r="AP10" s="90"/>
-      <c r="AQ10" s="90"/>
-      <c r="AR10" s="90"/>
-      <c r="AS10" s="90"/>
-      <c r="AT10" s="90"/>
-      <c r="AU10" s="90"/>
-      <c r="AV10" s="90"/>
+      <c r="AC10" s="89"/>
+      <c r="AD10" s="89"/>
+      <c r="AE10" s="89"/>
+      <c r="AF10" s="89"/>
+      <c r="AG10" s="89"/>
+      <c r="AH10" s="89"/>
+      <c r="AI10" s="89"/>
+      <c r="AJ10" s="89"/>
+      <c r="AK10" s="89"/>
+      <c r="AL10" s="89"/>
+      <c r="AM10" s="89"/>
+      <c r="AN10" s="89"/>
+      <c r="AO10" s="89"/>
+      <c r="AP10" s="89"/>
+      <c r="AQ10" s="89"/>
+      <c r="AR10" s="89"/>
+      <c r="AS10" s="89"/>
+      <c r="AT10" s="89"/>
+      <c r="AU10" s="89"/>
+      <c r="AV10" s="89"/>
       <c r="AW10" s="39"/>
       <c r="AX10" s="18"/>
     </row>
@@ -4935,18 +4935,18 @@
       <c r="H11" s="30">
         <v>5</v>
       </c>
-      <c r="I11" s="90" t="e">
+      <c r="I11" s="89" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="J11" s="90"/>
-      <c r="K11" s="90"/>
-      <c r="L11" s="90"/>
-      <c r="M11" s="90"/>
-      <c r="N11" s="90"/>
-      <c r="O11" s="90"/>
-      <c r="P11" s="90"/>
-      <c r="Q11" s="90"/>
+      <c r="J11" s="89"/>
+      <c r="K11" s="89"/>
+      <c r="L11" s="89"/>
+      <c r="M11" s="89"/>
+      <c r="N11" s="89"/>
+      <c r="O11" s="89"/>
+      <c r="P11" s="89"/>
+      <c r="Q11" s="89"/>
       <c r="R11"/>
       <c r="S11" s="30" t="s">
         <v>28</v>
@@ -4962,32 +4962,32 @@
       <c r="Z11" s="37"/>
       <c r="AA11" s="37"/>
       <c r="AB11"/>
-      <c r="AC11" s="90" t="e">
+      <c r="AC11" s="89" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="AD11" s="90"/>
-      <c r="AE11" s="90"/>
-      <c r="AF11" s="90"/>
-      <c r="AG11" s="90"/>
-      <c r="AH11" s="90"/>
-      <c r="AI11" s="90"/>
-      <c r="AJ11" s="90"/>
-      <c r="AK11" s="90"/>
-      <c r="AL11" s="90"/>
-      <c r="AM11" s="90"/>
-      <c r="AN11" s="90"/>
-      <c r="AO11" s="90"/>
-      <c r="AP11" s="90"/>
-      <c r="AQ11" s="90"/>
-      <c r="AR11" s="90"/>
-      <c r="AS11" s="90"/>
-      <c r="AT11" s="123" t="e">
+      <c r="AD11" s="89"/>
+      <c r="AE11" s="89"/>
+      <c r="AF11" s="89"/>
+      <c r="AG11" s="89"/>
+      <c r="AH11" s="89"/>
+      <c r="AI11" s="89"/>
+      <c r="AJ11" s="89"/>
+      <c r="AK11" s="89"/>
+      <c r="AL11" s="89"/>
+      <c r="AM11" s="89"/>
+      <c r="AN11" s="89"/>
+      <c r="AO11" s="89"/>
+      <c r="AP11" s="89"/>
+      <c r="AQ11" s="89"/>
+      <c r="AR11" s="89"/>
+      <c r="AS11" s="89"/>
+      <c r="AT11" s="125" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="AU11" s="123"/>
-      <c r="AV11" s="123"/>
+      <c r="AU11" s="125"/>
+      <c r="AV11" s="125"/>
       <c r="AW11" s="39"/>
       <c r="AX11" s="18"/>
     </row>
@@ -5002,18 +5002,18 @@
       <c r="H12" s="30">
         <v>6</v>
       </c>
-      <c r="I12" s="90" t="e">
+      <c r="I12" s="89" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="J12" s="90"/>
-      <c r="K12" s="90"/>
-      <c r="L12" s="90"/>
-      <c r="M12" s="90"/>
-      <c r="N12" s="90"/>
-      <c r="O12" s="90"/>
-      <c r="P12" s="90"/>
-      <c r="Q12" s="90"/>
+      <c r="J12" s="89"/>
+      <c r="K12" s="89"/>
+      <c r="L12" s="89"/>
+      <c r="M12" s="89"/>
+      <c r="N12" s="89"/>
+      <c r="O12" s="89"/>
+      <c r="P12" s="89"/>
+      <c r="Q12" s="89"/>
       <c r="R12"/>
       <c r="S12" s="30" t="s">
         <v>28</v>
@@ -5029,31 +5029,31 @@
       <c r="Z12" s="37"/>
       <c r="AA12" s="37"/>
       <c r="AB12" s="57"/>
-      <c r="AC12" s="90">
+      <c r="AC12" s="89">
         <v>5</v>
       </c>
-      <c r="AD12" s="90"/>
-      <c r="AE12" s="90"/>
-      <c r="AF12" s="90"/>
-      <c r="AG12" s="90"/>
-      <c r="AH12" s="90"/>
-      <c r="AI12" s="90"/>
-      <c r="AJ12" s="90"/>
-      <c r="AK12" s="90"/>
-      <c r="AL12" s="90"/>
-      <c r="AM12" s="90"/>
-      <c r="AN12" s="90"/>
-      <c r="AO12" s="90"/>
-      <c r="AP12" s="90"/>
-      <c r="AQ12" s="90"/>
-      <c r="AR12" s="90"/>
-      <c r="AS12" s="90"/>
-      <c r="AT12" s="123" t="e">
+      <c r="AD12" s="89"/>
+      <c r="AE12" s="89"/>
+      <c r="AF12" s="89"/>
+      <c r="AG12" s="89"/>
+      <c r="AH12" s="89"/>
+      <c r="AI12" s="89"/>
+      <c r="AJ12" s="89"/>
+      <c r="AK12" s="89"/>
+      <c r="AL12" s="89"/>
+      <c r="AM12" s="89"/>
+      <c r="AN12" s="89"/>
+      <c r="AO12" s="89"/>
+      <c r="AP12" s="89"/>
+      <c r="AQ12" s="89"/>
+      <c r="AR12" s="89"/>
+      <c r="AS12" s="89"/>
+      <c r="AT12" s="125" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="AU12" s="123"/>
-      <c r="AV12" s="123"/>
+      <c r="AU12" s="125"/>
+      <c r="AV12" s="125"/>
       <c r="AW12" s="39"/>
       <c r="AX12" s="18"/>
     </row>
@@ -5068,18 +5068,18 @@
       <c r="H13" s="30">
         <v>7</v>
       </c>
-      <c r="I13" s="90" t="e">
+      <c r="I13" s="89" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="J13" s="90"/>
-      <c r="K13" s="90"/>
-      <c r="L13" s="90"/>
-      <c r="M13" s="90"/>
-      <c r="N13" s="90"/>
-      <c r="O13" s="90"/>
-      <c r="P13" s="90"/>
-      <c r="Q13" s="90"/>
+      <c r="J13" s="89"/>
+      <c r="K13" s="89"/>
+      <c r="L13" s="89"/>
+      <c r="M13" s="89"/>
+      <c r="N13" s="89"/>
+      <c r="O13" s="89"/>
+      <c r="P13" s="89"/>
+      <c r="Q13" s="89"/>
       <c r="R13"/>
       <c r="S13" s="30" t="s">
         <v>28</v>
@@ -5100,27 +5100,27 @@
       <c r="AE13" s="30"/>
       <c r="AF13" s="30"/>
       <c r="AG13" s="30"/>
-      <c r="AH13" s="90" t="e">
+      <c r="AH13" s="89" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="AI13" s="90"/>
-      <c r="AJ13" s="90"/>
-      <c r="AK13" s="90"/>
-      <c r="AL13" s="90"/>
-      <c r="AM13" s="90"/>
-      <c r="AN13" s="90"/>
-      <c r="AO13" s="90"/>
-      <c r="AP13" s="90"/>
-      <c r="AQ13" s="90"/>
-      <c r="AR13" s="90"/>
-      <c r="AS13" s="90"/>
-      <c r="AT13" s="123" t="e">
+      <c r="AI13" s="89"/>
+      <c r="AJ13" s="89"/>
+      <c r="AK13" s="89"/>
+      <c r="AL13" s="89"/>
+      <c r="AM13" s="89"/>
+      <c r="AN13" s="89"/>
+      <c r="AO13" s="89"/>
+      <c r="AP13" s="89"/>
+      <c r="AQ13" s="89"/>
+      <c r="AR13" s="89"/>
+      <c r="AS13" s="89"/>
+      <c r="AT13" s="125" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="AU13" s="123"/>
-      <c r="AV13" s="123"/>
+      <c r="AU13" s="125"/>
+      <c r="AV13" s="125"/>
       <c r="AW13" s="39"/>
       <c r="AX13" s="18"/>
     </row>
@@ -5334,29 +5334,29 @@
     </row>
     <row r="18" spans="1:50" s="23" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A18" s="27"/>
-      <c r="B18" s="126" t="s">
+      <c r="B18" s="113" t="s">
         <v>35</v>
       </c>
-      <c r="C18" s="127"/>
-      <c r="D18" s="127"/>
-      <c r="E18" s="127"/>
-      <c r="F18" s="127"/>
-      <c r="G18" s="127"/>
-      <c r="H18" s="127"/>
-      <c r="I18" s="127"/>
-      <c r="J18" s="128"/>
-      <c r="K18" s="126" t="s">
+      <c r="C18" s="114"/>
+      <c r="D18" s="114"/>
+      <c r="E18" s="114"/>
+      <c r="F18" s="114"/>
+      <c r="G18" s="114"/>
+      <c r="H18" s="114"/>
+      <c r="I18" s="114"/>
+      <c r="J18" s="115"/>
+      <c r="K18" s="113" t="s">
         <v>44</v>
       </c>
-      <c r="L18" s="127"/>
-      <c r="M18" s="127"/>
-      <c r="N18" s="129"/>
-      <c r="O18" s="126" t="s">
+      <c r="L18" s="114"/>
+      <c r="M18" s="114"/>
+      <c r="N18" s="116"/>
+      <c r="O18" s="113" t="s">
         <v>37</v>
       </c>
-      <c r="P18" s="127"/>
-      <c r="Q18" s="127"/>
-      <c r="R18" s="129"/>
+      <c r="P18" s="114"/>
+      <c r="Q18" s="114"/>
+      <c r="R18" s="116"/>
       <c r="U18" s="79"/>
       <c r="V18"/>
       <c r="W18"/>
@@ -5390,29 +5390,29 @@
     </row>
     <row r="19" spans="1:50" s="20" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A19" s="27"/>
-      <c r="B19" s="130" t="s">
+      <c r="B19" s="134" t="s">
         <v>38</v>
       </c>
-      <c r="C19" s="131"/>
-      <c r="D19" s="131"/>
-      <c r="E19" s="131"/>
-      <c r="F19" s="131"/>
-      <c r="G19" s="131"/>
-      <c r="H19" s="131"/>
-      <c r="I19" s="131"/>
-      <c r="J19" s="174"/>
-      <c r="K19" s="175">
+      <c r="C19" s="135"/>
+      <c r="D19" s="135"/>
+      <c r="E19" s="135"/>
+      <c r="F19" s="135"/>
+      <c r="G19" s="135"/>
+      <c r="H19" s="135"/>
+      <c r="I19" s="135"/>
+      <c r="J19" s="136"/>
+      <c r="K19" s="137">
         <v>0</v>
       </c>
-      <c r="L19" s="131"/>
-      <c r="M19" s="131"/>
-      <c r="N19" s="174"/>
-      <c r="O19" s="176">
+      <c r="L19" s="135"/>
+      <c r="M19" s="135"/>
+      <c r="N19" s="136"/>
+      <c r="O19" s="138">
         <v>0</v>
       </c>
-      <c r="P19" s="124"/>
-      <c r="Q19" s="124"/>
-      <c r="R19" s="125"/>
+      <c r="P19" s="139"/>
+      <c r="Q19" s="139"/>
+      <c r="R19" s="140"/>
       <c r="U19" s="79"/>
       <c r="V19"/>
       <c r="W19"/>
@@ -5446,31 +5446,31 @@
     </row>
     <row r="20" spans="1:50" s="20" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A20" s="27"/>
-      <c r="B20" s="138" t="s">
+      <c r="B20" s="141" t="s">
         <v>39</v>
       </c>
-      <c r="C20" s="139"/>
-      <c r="D20" s="139"/>
-      <c r="E20" s="140"/>
-      <c r="F20" s="144" t="s">
+      <c r="C20" s="142"/>
+      <c r="D20" s="142"/>
+      <c r="E20" s="143"/>
+      <c r="F20" s="147" t="s">
         <v>45</v>
       </c>
-      <c r="G20" s="145"/>
-      <c r="H20" s="145"/>
-      <c r="I20" s="145"/>
-      <c r="J20" s="146"/>
-      <c r="K20" s="156">
+      <c r="G20" s="148"/>
+      <c r="H20" s="148"/>
+      <c r="I20" s="148"/>
+      <c r="J20" s="149"/>
+      <c r="K20" s="150">
         <v>500</v>
       </c>
-      <c r="L20" s="157"/>
-      <c r="M20" s="157"/>
-      <c r="N20" s="158"/>
-      <c r="O20" s="155">
+      <c r="L20" s="151"/>
+      <c r="M20" s="151"/>
+      <c r="N20" s="152"/>
+      <c r="O20" s="153">
         <v>1</v>
       </c>
-      <c r="P20" s="155"/>
-      <c r="Q20" s="155"/>
-      <c r="R20" s="155"/>
+      <c r="P20" s="153"/>
+      <c r="Q20" s="153"/>
+      <c r="R20" s="153"/>
       <c r="U20" s="79"/>
       <c r="V20"/>
       <c r="W20"/>
@@ -5504,29 +5504,29 @@
     </row>
     <row r="21" spans="1:50" s="20" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A21" s="27"/>
-      <c r="B21" s="141"/>
-      <c r="C21" s="142"/>
-      <c r="D21" s="142"/>
-      <c r="E21" s="143"/>
-      <c r="F21" s="144" t="s">
+      <c r="B21" s="144"/>
+      <c r="C21" s="145"/>
+      <c r="D21" s="145"/>
+      <c r="E21" s="146"/>
+      <c r="F21" s="147" t="s">
         <v>46</v>
       </c>
-      <c r="G21" s="145"/>
-      <c r="H21" s="145"/>
-      <c r="I21" s="145"/>
-      <c r="J21" s="146"/>
-      <c r="K21" s="156">
+      <c r="G21" s="148"/>
+      <c r="H21" s="148"/>
+      <c r="I21" s="148"/>
+      <c r="J21" s="149"/>
+      <c r="K21" s="150">
         <v>500</v>
       </c>
-      <c r="L21" s="157"/>
-      <c r="M21" s="157"/>
-      <c r="N21" s="158"/>
-      <c r="O21" s="159">
+      <c r="L21" s="151"/>
+      <c r="M21" s="151"/>
+      <c r="N21" s="152"/>
+      <c r="O21" s="154">
         <v>5</v>
       </c>
-      <c r="P21" s="160"/>
-      <c r="Q21" s="160"/>
-      <c r="R21" s="161"/>
+      <c r="P21" s="155"/>
+      <c r="Q21" s="155"/>
+      <c r="R21" s="156"/>
       <c r="U21" s="79"/>
       <c r="V21"/>
       <c r="W21"/>
@@ -5560,31 +5560,31 @@
     </row>
     <row r="22" spans="1:50" s="20" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A22" s="27"/>
-      <c r="B22" s="138" t="s">
+      <c r="B22" s="141" t="s">
         <v>40</v>
       </c>
-      <c r="C22" s="139"/>
-      <c r="D22" s="139"/>
-      <c r="E22" s="140"/>
-      <c r="F22" s="144" t="s">
+      <c r="C22" s="142"/>
+      <c r="D22" s="142"/>
+      <c r="E22" s="143"/>
+      <c r="F22" s="147" t="s">
         <v>45</v>
       </c>
-      <c r="G22" s="145"/>
-      <c r="H22" s="145"/>
-      <c r="I22" s="145"/>
-      <c r="J22" s="146"/>
-      <c r="K22" s="171">
+      <c r="G22" s="148"/>
+      <c r="H22" s="148"/>
+      <c r="I22" s="148"/>
+      <c r="J22" s="149"/>
+      <c r="K22" s="168">
         <v>1000</v>
       </c>
-      <c r="L22" s="171"/>
-      <c r="M22" s="171"/>
-      <c r="N22" s="171"/>
-      <c r="O22" s="155">
+      <c r="L22" s="168"/>
+      <c r="M22" s="168"/>
+      <c r="N22" s="168"/>
+      <c r="O22" s="153">
         <v>1</v>
       </c>
-      <c r="P22" s="155"/>
-      <c r="Q22" s="155"/>
-      <c r="R22" s="155"/>
+      <c r="P22" s="153"/>
+      <c r="Q22" s="153"/>
+      <c r="R22" s="153"/>
       <c r="S22" s="79"/>
       <c r="T22" s="79"/>
       <c r="U22" s="79"/>
@@ -5620,29 +5620,29 @@
     </row>
     <row r="23" spans="1:50" s="20" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A23" s="27"/>
-      <c r="B23" s="141"/>
-      <c r="C23" s="142"/>
-      <c r="D23" s="142"/>
-      <c r="E23" s="143"/>
-      <c r="F23" s="144" t="s">
+      <c r="B23" s="144"/>
+      <c r="C23" s="145"/>
+      <c r="D23" s="145"/>
+      <c r="E23" s="146"/>
+      <c r="F23" s="147" t="s">
         <v>46</v>
       </c>
-      <c r="G23" s="145"/>
-      <c r="H23" s="145"/>
-      <c r="I23" s="145"/>
-      <c r="J23" s="146"/>
-      <c r="K23" s="171">
+      <c r="G23" s="148"/>
+      <c r="H23" s="148"/>
+      <c r="I23" s="148"/>
+      <c r="J23" s="149"/>
+      <c r="K23" s="168">
         <v>1000</v>
       </c>
-      <c r="L23" s="171"/>
-      <c r="M23" s="171"/>
-      <c r="N23" s="171"/>
-      <c r="O23" s="155">
+      <c r="L23" s="168"/>
+      <c r="M23" s="168"/>
+      <c r="N23" s="168"/>
+      <c r="O23" s="153">
         <v>10</v>
       </c>
-      <c r="P23" s="155"/>
-      <c r="Q23" s="155"/>
-      <c r="R23" s="155"/>
+      <c r="P23" s="153"/>
+      <c r="Q23" s="153"/>
+      <c r="R23" s="153"/>
       <c r="S23" s="79"/>
       <c r="T23" s="79"/>
       <c r="U23" s="79"/>
@@ -5678,31 +5678,31 @@
     </row>
     <row r="24" spans="1:50" s="20" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A24" s="21"/>
-      <c r="B24" s="138" t="s">
+      <c r="B24" s="141" t="s">
         <v>41</v>
       </c>
-      <c r="C24" s="139"/>
-      <c r="D24" s="139"/>
-      <c r="E24" s="140"/>
-      <c r="F24" s="144" t="s">
+      <c r="C24" s="142"/>
+      <c r="D24" s="142"/>
+      <c r="E24" s="143"/>
+      <c r="F24" s="147" t="s">
         <v>47</v>
       </c>
-      <c r="G24" s="145"/>
-      <c r="H24" s="145"/>
-      <c r="I24" s="145"/>
-      <c r="J24" s="146"/>
-      <c r="K24" s="162">
+      <c r="G24" s="148"/>
+      <c r="H24" s="148"/>
+      <c r="I24" s="148"/>
+      <c r="J24" s="149"/>
+      <c r="K24" s="157">
         <v>500</v>
       </c>
-      <c r="L24" s="163"/>
-      <c r="M24" s="163"/>
-      <c r="N24" s="164"/>
-      <c r="O24" s="165">
+      <c r="L24" s="158"/>
+      <c r="M24" s="158"/>
+      <c r="N24" s="159"/>
+      <c r="O24" s="160">
         <v>1</v>
       </c>
-      <c r="P24" s="166"/>
-      <c r="Q24" s="166"/>
-      <c r="R24" s="167"/>
+      <c r="P24" s="161"/>
+      <c r="Q24" s="161"/>
+      <c r="R24" s="162"/>
       <c r="S24"/>
       <c r="T24"/>
       <c r="U24"/>
@@ -5738,29 +5738,29 @@
     </row>
     <row r="25" spans="1:50" s="20" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A25" s="21"/>
-      <c r="B25" s="141"/>
-      <c r="C25" s="142"/>
-      <c r="D25" s="142"/>
-      <c r="E25" s="143"/>
-      <c r="F25" s="144" t="s">
+      <c r="B25" s="144"/>
+      <c r="C25" s="145"/>
+      <c r="D25" s="145"/>
+      <c r="E25" s="146"/>
+      <c r="F25" s="147" t="s">
         <v>46</v>
       </c>
-      <c r="G25" s="145"/>
-      <c r="H25" s="145"/>
-      <c r="I25" s="145"/>
-      <c r="J25" s="146"/>
-      <c r="K25" s="150">
+      <c r="G25" s="148"/>
+      <c r="H25" s="148"/>
+      <c r="I25" s="148"/>
+      <c r="J25" s="149"/>
+      <c r="K25" s="163">
         <v>500</v>
       </c>
-      <c r="L25" s="145"/>
-      <c r="M25" s="145"/>
-      <c r="N25" s="151"/>
-      <c r="O25" s="168">
+      <c r="L25" s="148"/>
+      <c r="M25" s="148"/>
+      <c r="N25" s="164"/>
+      <c r="O25" s="165">
         <v>5</v>
       </c>
-      <c r="P25" s="169"/>
-      <c r="Q25" s="169"/>
-      <c r="R25" s="170"/>
+      <c r="P25" s="166"/>
+      <c r="Q25" s="166"/>
+      <c r="R25" s="167"/>
       <c r="S25"/>
       <c r="T25"/>
       <c r="U25"/>
@@ -5796,31 +5796,31 @@
     </row>
     <row r="26" spans="1:50" s="16" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A26" s="22"/>
-      <c r="B26" s="138" t="s">
+      <c r="B26" s="141" t="s">
         <v>48</v>
       </c>
-      <c r="C26" s="139"/>
-      <c r="D26" s="139"/>
-      <c r="E26" s="140"/>
-      <c r="F26" s="144" t="s">
+      <c r="C26" s="142"/>
+      <c r="D26" s="142"/>
+      <c r="E26" s="143"/>
+      <c r="F26" s="147" t="s">
         <v>47</v>
       </c>
-      <c r="G26" s="145"/>
-      <c r="H26" s="145"/>
-      <c r="I26" s="145"/>
-      <c r="J26" s="146"/>
-      <c r="K26" s="147">
+      <c r="G26" s="148"/>
+      <c r="H26" s="148"/>
+      <c r="I26" s="148"/>
+      <c r="J26" s="149"/>
+      <c r="K26" s="169">
         <v>0</v>
       </c>
-      <c r="L26" s="148"/>
-      <c r="M26" s="148"/>
-      <c r="N26" s="149"/>
-      <c r="O26" s="134">
+      <c r="L26" s="170"/>
+      <c r="M26" s="170"/>
+      <c r="N26" s="171"/>
+      <c r="O26" s="172">
         <v>1</v>
       </c>
-      <c r="P26" s="135"/>
-      <c r="Q26" s="135"/>
-      <c r="R26" s="136"/>
+      <c r="P26" s="173"/>
+      <c r="Q26" s="173"/>
+      <c r="R26" s="174"/>
       <c r="S26"/>
       <c r="T26"/>
       <c r="U26"/>
@@ -5856,27 +5856,27 @@
     </row>
     <row r="27" spans="1:50" s="20" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A27" s="31"/>
-      <c r="B27" s="141"/>
-      <c r="C27" s="142"/>
-      <c r="D27" s="142"/>
-      <c r="E27" s="143"/>
-      <c r="F27" s="144" t="s">
+      <c r="B27" s="144"/>
+      <c r="C27" s="145"/>
+      <c r="D27" s="145"/>
+      <c r="E27" s="146"/>
+      <c r="F27" s="147" t="s">
         <v>49</v>
       </c>
-      <c r="G27" s="145"/>
-      <c r="H27" s="145"/>
-      <c r="I27" s="145"/>
-      <c r="J27" s="146"/>
-      <c r="K27" s="147">
+      <c r="G27" s="148"/>
+      <c r="H27" s="148"/>
+      <c r="I27" s="148"/>
+      <c r="J27" s="149"/>
+      <c r="K27" s="169">
         <v>0</v>
       </c>
-      <c r="L27" s="148"/>
-      <c r="M27" s="148"/>
-      <c r="N27" s="149"/>
-      <c r="O27" s="134"/>
-      <c r="P27" s="135"/>
-      <c r="Q27" s="135"/>
-      <c r="R27" s="136"/>
+      <c r="L27" s="170"/>
+      <c r="M27" s="170"/>
+      <c r="N27" s="171"/>
+      <c r="O27" s="172"/>
+      <c r="P27" s="173"/>
+      <c r="Q27" s="173"/>
+      <c r="R27" s="174"/>
       <c r="S27"/>
       <c r="T27"/>
       <c r="U27"/>
@@ -5912,23 +5912,23 @@
     </row>
     <row r="28" spans="1:50" s="20" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A28" s="31"/>
-      <c r="B28" s="138"/>
-      <c r="C28" s="139"/>
-      <c r="D28" s="139"/>
-      <c r="E28" s="140"/>
-      <c r="F28" s="144"/>
-      <c r="G28" s="145"/>
-      <c r="H28" s="145"/>
-      <c r="I28" s="145"/>
-      <c r="J28" s="146"/>
-      <c r="K28" s="147"/>
-      <c r="L28" s="148"/>
-      <c r="M28" s="148"/>
-      <c r="N28" s="149"/>
-      <c r="O28" s="134"/>
-      <c r="P28" s="135"/>
-      <c r="Q28" s="135"/>
-      <c r="R28" s="136"/>
+      <c r="B28" s="141"/>
+      <c r="C28" s="142"/>
+      <c r="D28" s="142"/>
+      <c r="E28" s="143"/>
+      <c r="F28" s="147"/>
+      <c r="G28" s="148"/>
+      <c r="H28" s="148"/>
+      <c r="I28" s="148"/>
+      <c r="J28" s="149"/>
+      <c r="K28" s="169"/>
+      <c r="L28" s="170"/>
+      <c r="M28" s="170"/>
+      <c r="N28" s="171"/>
+      <c r="O28" s="172"/>
+      <c r="P28" s="173"/>
+      <c r="Q28" s="173"/>
+      <c r="R28" s="174"/>
       <c r="S28"/>
       <c r="T28"/>
       <c r="U28"/>
@@ -5964,137 +5964,137 @@
     </row>
     <row r="29" spans="1:50" s="8" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A29" s="31"/>
-      <c r="B29" s="141"/>
-      <c r="C29" s="142"/>
-      <c r="D29" s="142"/>
-      <c r="E29" s="143"/>
-      <c r="F29" s="144"/>
-      <c r="G29" s="145"/>
-      <c r="H29" s="145"/>
-      <c r="I29" s="145"/>
-      <c r="J29" s="146"/>
-      <c r="K29" s="150"/>
-      <c r="L29" s="145"/>
-      <c r="M29" s="145"/>
-      <c r="N29" s="151"/>
-      <c r="O29" s="134"/>
-      <c r="P29" s="135"/>
-      <c r="Q29" s="135"/>
-      <c r="R29" s="136"/>
+      <c r="B29" s="144"/>
+      <c r="C29" s="145"/>
+      <c r="D29" s="145"/>
+      <c r="E29" s="146"/>
+      <c r="F29" s="147"/>
+      <c r="G29" s="148"/>
+      <c r="H29" s="148"/>
+      <c r="I29" s="148"/>
+      <c r="J29" s="149"/>
+      <c r="K29" s="163"/>
+      <c r="L29" s="148"/>
+      <c r="M29" s="148"/>
+      <c r="N29" s="164"/>
+      <c r="O29" s="172"/>
+      <c r="P29" s="173"/>
+      <c r="Q29" s="173"/>
+      <c r="R29" s="174"/>
       <c r="S29"/>
-      <c r="T29" s="120" t="s">
+      <c r="T29" s="131" t="s">
         <v>50</v>
       </c>
-      <c r="U29" s="121"/>
-      <c r="V29" s="121"/>
-      <c r="W29" s="121"/>
-      <c r="X29" s="121"/>
-      <c r="Y29" s="121"/>
-      <c r="Z29" s="121"/>
-      <c r="AA29" s="121"/>
-      <c r="AB29" s="121"/>
-      <c r="AC29" s="121"/>
-      <c r="AD29" s="121"/>
-      <c r="AE29" s="121"/>
-      <c r="AF29" s="121"/>
-      <c r="AG29" s="121"/>
-      <c r="AH29" s="121"/>
-      <c r="AI29" s="121"/>
-      <c r="AJ29" s="121"/>
-      <c r="AK29" s="121"/>
-      <c r="AL29" s="121"/>
-      <c r="AM29" s="121"/>
-      <c r="AN29" s="121"/>
-      <c r="AO29" s="121"/>
-      <c r="AP29" s="121"/>
-      <c r="AQ29" s="121"/>
-      <c r="AR29" s="121"/>
-      <c r="AS29" s="121"/>
-      <c r="AT29" s="121"/>
-      <c r="AU29" s="121"/>
-      <c r="AV29" s="121"/>
-      <c r="AW29" s="122"/>
+      <c r="U29" s="132"/>
+      <c r="V29" s="132"/>
+      <c r="W29" s="132"/>
+      <c r="X29" s="132"/>
+      <c r="Y29" s="132"/>
+      <c r="Z29" s="132"/>
+      <c r="AA29" s="132"/>
+      <c r="AB29" s="132"/>
+      <c r="AC29" s="132"/>
+      <c r="AD29" s="132"/>
+      <c r="AE29" s="132"/>
+      <c r="AF29" s="132"/>
+      <c r="AG29" s="132"/>
+      <c r="AH29" s="132"/>
+      <c r="AI29" s="132"/>
+      <c r="AJ29" s="132"/>
+      <c r="AK29" s="132"/>
+      <c r="AL29" s="132"/>
+      <c r="AM29" s="132"/>
+      <c r="AN29" s="132"/>
+      <c r="AO29" s="132"/>
+      <c r="AP29" s="132"/>
+      <c r="AQ29" s="132"/>
+      <c r="AR29" s="132"/>
+      <c r="AS29" s="132"/>
+      <c r="AT29" s="132"/>
+      <c r="AU29" s="132"/>
+      <c r="AV29" s="132"/>
+      <c r="AW29" s="133"/>
       <c r="AX29" s="18"/>
     </row>
     <row r="30" spans="1:50" ht="20.100000000000001" customHeight="1">
       <c r="A30" s="31"/>
-      <c r="B30" s="138"/>
-      <c r="C30" s="139"/>
-      <c r="D30" s="139"/>
-      <c r="E30" s="140"/>
-      <c r="F30" s="144"/>
-      <c r="G30" s="145"/>
-      <c r="H30" s="145"/>
-      <c r="I30" s="145"/>
-      <c r="J30" s="146"/>
-      <c r="K30" s="150"/>
-      <c r="L30" s="145"/>
-      <c r="M30" s="145"/>
-      <c r="N30" s="151"/>
-      <c r="O30" s="134"/>
-      <c r="P30" s="135"/>
-      <c r="Q30" s="135"/>
-      <c r="R30" s="136"/>
+      <c r="B30" s="141"/>
+      <c r="C30" s="142"/>
+      <c r="D30" s="142"/>
+      <c r="E30" s="143"/>
+      <c r="F30" s="147"/>
+      <c r="G30" s="148"/>
+      <c r="H30" s="148"/>
+      <c r="I30" s="148"/>
+      <c r="J30" s="149"/>
+      <c r="K30" s="163"/>
+      <c r="L30" s="148"/>
+      <c r="M30" s="148"/>
+      <c r="N30" s="164"/>
+      <c r="O30" s="172"/>
+      <c r="P30" s="173"/>
+      <c r="Q30" s="173"/>
+      <c r="R30" s="174"/>
       <c r="S30"/>
-      <c r="T30" s="152" t="s">
+      <c r="T30" s="175" t="s">
         <v>5</v>
       </c>
-      <c r="U30" s="153"/>
-      <c r="V30" s="153"/>
-      <c r="W30" s="153"/>
-      <c r="X30" s="153"/>
-      <c r="Y30" s="153"/>
-      <c r="Z30" s="153"/>
-      <c r="AA30" s="153"/>
-      <c r="AB30" s="154" t="s">
+      <c r="U30" s="128"/>
+      <c r="V30" s="128"/>
+      <c r="W30" s="128"/>
+      <c r="X30" s="128"/>
+      <c r="Y30" s="128"/>
+      <c r="Z30" s="128"/>
+      <c r="AA30" s="128"/>
+      <c r="AB30" s="127" t="s">
         <v>51</v>
       </c>
-      <c r="AC30" s="154"/>
-      <c r="AD30" s="154"/>
-      <c r="AE30" s="154" t="s">
+      <c r="AC30" s="127"/>
+      <c r="AD30" s="127"/>
+      <c r="AE30" s="127" t="s">
         <v>19</v>
       </c>
-      <c r="AF30" s="154"/>
-      <c r="AG30" s="154"/>
+      <c r="AF30" s="127"/>
+      <c r="AG30" s="127"/>
       <c r="AH30" s="80"/>
       <c r="AI30" s="80"/>
       <c r="AJ30" s="80"/>
-      <c r="AK30" s="153" t="s">
+      <c r="AK30" s="128" t="s">
         <v>32</v>
       </c>
-      <c r="AL30" s="153"/>
-      <c r="AM30" s="153"/>
-      <c r="AN30" s="153"/>
-      <c r="AO30" s="153"/>
-      <c r="AP30" s="153"/>
-      <c r="AQ30" s="153"/>
-      <c r="AR30" s="153"/>
-      <c r="AS30" s="153"/>
-      <c r="AT30" s="153"/>
-      <c r="AU30" s="153"/>
-      <c r="AV30" s="153"/>
-      <c r="AW30" s="172"/>
+      <c r="AL30" s="128"/>
+      <c r="AM30" s="128"/>
+      <c r="AN30" s="128"/>
+      <c r="AO30" s="128"/>
+      <c r="AP30" s="128"/>
+      <c r="AQ30" s="128"/>
+      <c r="AR30" s="128"/>
+      <c r="AS30" s="128"/>
+      <c r="AT30" s="128"/>
+      <c r="AU30" s="128"/>
+      <c r="AV30" s="128"/>
+      <c r="AW30" s="129"/>
       <c r="AX30" s="18"/>
     </row>
     <row r="31" spans="1:50" ht="23.25" customHeight="1">
       <c r="A31" s="31"/>
-      <c r="B31" s="141"/>
-      <c r="C31" s="142"/>
-      <c r="D31" s="142"/>
-      <c r="E31" s="143"/>
-      <c r="F31" s="144"/>
-      <c r="G31" s="145"/>
-      <c r="H31" s="145"/>
-      <c r="I31" s="145"/>
-      <c r="J31" s="146"/>
-      <c r="K31" s="147"/>
-      <c r="L31" s="148"/>
-      <c r="M31" s="148"/>
-      <c r="N31" s="149"/>
-      <c r="O31" s="134"/>
-      <c r="P31" s="135"/>
-      <c r="Q31" s="135"/>
-      <c r="R31" s="136"/>
+      <c r="B31" s="144"/>
+      <c r="C31" s="145"/>
+      <c r="D31" s="145"/>
+      <c r="E31" s="146"/>
+      <c r="F31" s="147"/>
+      <c r="G31" s="148"/>
+      <c r="H31" s="148"/>
+      <c r="I31" s="148"/>
+      <c r="J31" s="149"/>
+      <c r="K31" s="169"/>
+      <c r="L31" s="170"/>
+      <c r="M31" s="170"/>
+      <c r="N31" s="171"/>
+      <c r="O31" s="172"/>
+      <c r="P31" s="173"/>
+      <c r="Q31" s="173"/>
+      <c r="R31" s="174"/>
       <c r="S31"/>
       <c r="T31" s="81">
         <v>1</v>
@@ -6109,174 +6109,174 @@
       <c r="Y31" s="88"/>
       <c r="Z31" s="88"/>
       <c r="AA31" s="88"/>
-      <c r="AB31" s="173" t="e">
+      <c r="AB31" s="130" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="AC31" s="173"/>
-      <c r="AD31" s="173"/>
+      <c r="AC31" s="130"/>
+      <c r="AD31" s="130"/>
       <c r="AE31" s="88" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
       <c r="AF31" s="88"/>
       <c r="AG31" s="88"/>
-      <c r="AH31" s="91" t="e">
+      <c r="AH31" s="126" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="AI31" s="91"/>
-      <c r="AJ31" s="91"/>
-      <c r="AK31" s="115" t="s">
+      <c r="AI31" s="126"/>
+      <c r="AJ31" s="126"/>
+      <c r="AK31" s="109" t="s">
         <v>52</v>
       </c>
-      <c r="AL31" s="115"/>
-      <c r="AM31" s="115"/>
-      <c r="AN31" s="115"/>
-      <c r="AO31" s="115"/>
-      <c r="AP31" s="115"/>
-      <c r="AQ31" s="115"/>
-      <c r="AR31" s="115"/>
-      <c r="AS31" s="115"/>
-      <c r="AT31" s="115"/>
-      <c r="AU31" s="115"/>
-      <c r="AV31" s="115"/>
+      <c r="AL31" s="109"/>
+      <c r="AM31" s="109"/>
+      <c r="AN31" s="109"/>
+      <c r="AO31" s="109"/>
+      <c r="AP31" s="109"/>
+      <c r="AQ31" s="109"/>
+      <c r="AR31" s="109"/>
+      <c r="AS31" s="109"/>
+      <c r="AT31" s="109"/>
+      <c r="AU31" s="109"/>
+      <c r="AV31" s="109"/>
       <c r="AW31" s="38"/>
       <c r="AX31" s="18"/>
     </row>
     <row r="32" spans="1:50" s="6" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A32" s="31"/>
-      <c r="B32" s="138"/>
-      <c r="C32" s="139"/>
-      <c r="D32" s="139"/>
-      <c r="E32" s="140"/>
-      <c r="F32" s="144"/>
-      <c r="G32" s="145"/>
-      <c r="H32" s="145"/>
-      <c r="I32" s="145"/>
-      <c r="J32" s="146"/>
-      <c r="K32" s="147"/>
-      <c r="L32" s="148"/>
-      <c r="M32" s="148"/>
-      <c r="N32" s="149"/>
-      <c r="O32" s="134"/>
-      <c r="P32" s="135"/>
-      <c r="Q32" s="135"/>
-      <c r="R32" s="136"/>
+      <c r="B32" s="141"/>
+      <c r="C32" s="142"/>
+      <c r="D32" s="142"/>
+      <c r="E32" s="143"/>
+      <c r="F32" s="147"/>
+      <c r="G32" s="148"/>
+      <c r="H32" s="148"/>
+      <c r="I32" s="148"/>
+      <c r="J32" s="149"/>
+      <c r="K32" s="169"/>
+      <c r="L32" s="170"/>
+      <c r="M32" s="170"/>
+      <c r="N32" s="171"/>
+      <c r="O32" s="172"/>
+      <c r="P32" s="173"/>
+      <c r="Q32" s="173"/>
+      <c r="R32" s="174"/>
       <c r="S32"/>
       <c r="T32" s="82">
         <v>2</v>
       </c>
-      <c r="U32" s="90" t="e">
+      <c r="U32" s="89" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="V32" s="90"/>
-      <c r="W32" s="90"/>
-      <c r="X32" s="90"/>
-      <c r="Y32" s="90"/>
-      <c r="Z32" s="90"/>
-      <c r="AA32" s="90"/>
-      <c r="AB32" s="137" t="e">
+      <c r="V32" s="89"/>
+      <c r="W32" s="89"/>
+      <c r="X32" s="89"/>
+      <c r="Y32" s="89"/>
+      <c r="Z32" s="89"/>
+      <c r="AA32" s="89"/>
+      <c r="AB32" s="124" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="AC32" s="137"/>
-      <c r="AD32" s="137"/>
+      <c r="AC32" s="124"/>
+      <c r="AD32" s="124"/>
       <c r="AE32" s="88" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
       <c r="AF32" s="88"/>
       <c r="AG32" s="88"/>
-      <c r="AH32" s="91" t="e">
+      <c r="AH32" s="126" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="AI32" s="91"/>
-      <c r="AJ32" s="91"/>
-      <c r="AK32" s="90" t="s">
+      <c r="AI32" s="126"/>
+      <c r="AJ32" s="126"/>
+      <c r="AK32" s="89" t="s">
         <v>53</v>
       </c>
-      <c r="AL32" s="90"/>
-      <c r="AM32" s="90"/>
-      <c r="AN32" s="90"/>
-      <c r="AO32" s="90"/>
-      <c r="AP32" s="90"/>
-      <c r="AQ32" s="90"/>
-      <c r="AR32" s="90"/>
-      <c r="AS32" s="90"/>
-      <c r="AT32" s="90"/>
-      <c r="AU32" s="90"/>
-      <c r="AV32" s="90"/>
+      <c r="AL32" s="89"/>
+      <c r="AM32" s="89"/>
+      <c r="AN32" s="89"/>
+      <c r="AO32" s="89"/>
+      <c r="AP32" s="89"/>
+      <c r="AQ32" s="89"/>
+      <c r="AR32" s="89"/>
+      <c r="AS32" s="89"/>
+      <c r="AT32" s="89"/>
+      <c r="AU32" s="89"/>
+      <c r="AV32" s="89"/>
       <c r="AW32" s="38"/>
       <c r="AX32" s="18"/>
     </row>
     <row r="33" spans="1:50" s="6" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A33" s="31"/>
-      <c r="B33" s="141"/>
-      <c r="C33" s="142"/>
-      <c r="D33" s="142"/>
-      <c r="E33" s="143"/>
-      <c r="F33" s="144"/>
-      <c r="G33" s="145"/>
-      <c r="H33" s="145"/>
-      <c r="I33" s="145"/>
-      <c r="J33" s="146"/>
-      <c r="K33" s="147"/>
-      <c r="L33" s="148"/>
-      <c r="M33" s="148"/>
-      <c r="N33" s="149"/>
-      <c r="O33" s="134"/>
-      <c r="P33" s="135"/>
-      <c r="Q33" s="135"/>
-      <c r="R33" s="136"/>
+      <c r="B33" s="144"/>
+      <c r="C33" s="145"/>
+      <c r="D33" s="145"/>
+      <c r="E33" s="146"/>
+      <c r="F33" s="147"/>
+      <c r="G33" s="148"/>
+      <c r="H33" s="148"/>
+      <c r="I33" s="148"/>
+      <c r="J33" s="149"/>
+      <c r="K33" s="169"/>
+      <c r="L33" s="170"/>
+      <c r="M33" s="170"/>
+      <c r="N33" s="171"/>
+      <c r="O33" s="172"/>
+      <c r="P33" s="173"/>
+      <c r="Q33" s="173"/>
+      <c r="R33" s="174"/>
       <c r="S33"/>
       <c r="T33" s="82">
         <v>3</v>
       </c>
-      <c r="U33" s="90" t="e">
+      <c r="U33" s="89" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="V33" s="90"/>
-      <c r="W33" s="90"/>
-      <c r="X33" s="90"/>
-      <c r="Y33" s="90"/>
-      <c r="Z33" s="90"/>
-      <c r="AA33" s="90"/>
-      <c r="AB33" s="137" t="e">
+      <c r="V33" s="89"/>
+      <c r="W33" s="89"/>
+      <c r="X33" s="89"/>
+      <c r="Y33" s="89"/>
+      <c r="Z33" s="89"/>
+      <c r="AA33" s="89"/>
+      <c r="AB33" s="124" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="AC33" s="137"/>
-      <c r="AD33" s="137"/>
+      <c r="AC33" s="124"/>
+      <c r="AD33" s="124"/>
       <c r="AE33" s="88" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
       <c r="AF33" s="88"/>
       <c r="AG33" s="88"/>
-      <c r="AH33" s="91" t="e">
+      <c r="AH33" s="126" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="AI33" s="91"/>
-      <c r="AJ33" s="91"/>
-      <c r="AK33" s="90" t="s">
+      <c r="AI33" s="126"/>
+      <c r="AJ33" s="126"/>
+      <c r="AK33" s="89" t="s">
         <v>54</v>
       </c>
-      <c r="AL33" s="90"/>
-      <c r="AM33" s="90"/>
-      <c r="AN33" s="90"/>
-      <c r="AO33" s="90"/>
-      <c r="AP33" s="90"/>
-      <c r="AQ33" s="90"/>
-      <c r="AR33" s="90"/>
-      <c r="AS33" s="90"/>
-      <c r="AT33" s="90"/>
-      <c r="AU33" s="90"/>
-      <c r="AV33" s="90"/>
+      <c r="AL33" s="89"/>
+      <c r="AM33" s="89"/>
+      <c r="AN33" s="89"/>
+      <c r="AO33" s="89"/>
+      <c r="AP33" s="89"/>
+      <c r="AQ33" s="89"/>
+      <c r="AR33" s="89"/>
+      <c r="AS33" s="89"/>
+      <c r="AT33" s="89"/>
+      <c r="AU33" s="89"/>
+      <c r="AV33" s="89"/>
       <c r="AW33" s="38"/>
       <c r="AX33" s="18"/>
     </row>
@@ -6303,48 +6303,48 @@
       <c r="T34" s="82">
         <v>4</v>
       </c>
-      <c r="U34" s="90" t="e">
+      <c r="U34" s="89" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="V34" s="90"/>
-      <c r="W34" s="90"/>
-      <c r="X34" s="90"/>
-      <c r="Y34" s="90"/>
-      <c r="Z34" s="90"/>
-      <c r="AA34" s="90"/>
-      <c r="AB34" s="137" t="e">
+      <c r="V34" s="89"/>
+      <c r="W34" s="89"/>
+      <c r="X34" s="89"/>
+      <c r="Y34" s="89"/>
+      <c r="Z34" s="89"/>
+      <c r="AA34" s="89"/>
+      <c r="AB34" s="124" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="AC34" s="137"/>
-      <c r="AD34" s="137"/>
+      <c r="AC34" s="124"/>
+      <c r="AD34" s="124"/>
       <c r="AE34" s="88" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
       <c r="AF34" s="88"/>
       <c r="AG34" s="88"/>
-      <c r="AH34" s="91" t="e">
+      <c r="AH34" s="126" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="AI34" s="91"/>
-      <c r="AJ34" s="91"/>
-      <c r="AK34" s="90" t="s">
+      <c r="AI34" s="126"/>
+      <c r="AJ34" s="126"/>
+      <c r="AK34" s="89" t="s">
         <v>52</v>
       </c>
-      <c r="AL34" s="90"/>
-      <c r="AM34" s="90"/>
-      <c r="AN34" s="90"/>
-      <c r="AO34" s="90"/>
-      <c r="AP34" s="90"/>
-      <c r="AQ34" s="90"/>
-      <c r="AR34" s="90"/>
-      <c r="AS34" s="90"/>
-      <c r="AT34" s="90"/>
-      <c r="AU34" s="90"/>
-      <c r="AV34" s="90"/>
+      <c r="AL34" s="89"/>
+      <c r="AM34" s="89"/>
+      <c r="AN34" s="89"/>
+      <c r="AO34" s="89"/>
+      <c r="AP34" s="89"/>
+      <c r="AQ34" s="89"/>
+      <c r="AR34" s="89"/>
+      <c r="AS34" s="89"/>
+      <c r="AT34" s="89"/>
+      <c r="AU34" s="89"/>
+      <c r="AV34" s="89"/>
       <c r="AW34" s="38"/>
       <c r="AX34" s="18"/>
     </row>
@@ -6371,46 +6371,46 @@
       <c r="T35" s="82">
         <v>5</v>
       </c>
-      <c r="U35" s="90" t="e">
+      <c r="U35" s="89" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="V35" s="90"/>
-      <c r="W35" s="90"/>
-      <c r="X35" s="90"/>
-      <c r="Y35" s="90"/>
-      <c r="Z35" s="90"/>
-      <c r="AA35" s="90"/>
-      <c r="AB35" s="137" t="e">
+      <c r="V35" s="89"/>
+      <c r="W35" s="89"/>
+      <c r="X35" s="89"/>
+      <c r="Y35" s="89"/>
+      <c r="Z35" s="89"/>
+      <c r="AA35" s="89"/>
+      <c r="AB35" s="124" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="AC35" s="137"/>
-      <c r="AD35" s="137"/>
+      <c r="AC35" s="124"/>
+      <c r="AD35" s="124"/>
       <c r="AE35" s="88" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
       <c r="AF35" s="88"/>
       <c r="AG35" s="88"/>
-      <c r="AH35" s="91" t="e">
+      <c r="AH35" s="126" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="AI35" s="91"/>
-      <c r="AJ35" s="91"/>
-      <c r="AK35" s="90"/>
-      <c r="AL35" s="90"/>
-      <c r="AM35" s="90"/>
-      <c r="AN35" s="90"/>
-      <c r="AO35" s="90"/>
-      <c r="AP35" s="90"/>
-      <c r="AQ35" s="90"/>
-      <c r="AR35" s="90"/>
-      <c r="AS35" s="90"/>
-      <c r="AT35" s="90"/>
-      <c r="AU35" s="90"/>
-      <c r="AV35" s="90"/>
+      <c r="AI35" s="126"/>
+      <c r="AJ35" s="126"/>
+      <c r="AK35" s="89"/>
+      <c r="AL35" s="89"/>
+      <c r="AM35" s="89"/>
+      <c r="AN35" s="89"/>
+      <c r="AO35" s="89"/>
+      <c r="AP35" s="89"/>
+      <c r="AQ35" s="89"/>
+      <c r="AR35" s="89"/>
+      <c r="AS35" s="89"/>
+      <c r="AT35" s="89"/>
+      <c r="AU35" s="89"/>
+      <c r="AV35" s="89"/>
       <c r="AW35" s="38"/>
       <c r="AX35" s="18"/>
     </row>
@@ -6437,46 +6437,46 @@
       <c r="T36" s="82">
         <v>6</v>
       </c>
-      <c r="U36" s="90" t="e">
+      <c r="U36" s="89" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="V36" s="90"/>
-      <c r="W36" s="90"/>
-      <c r="X36" s="90"/>
-      <c r="Y36" s="90"/>
-      <c r="Z36" s="90"/>
-      <c r="AA36" s="90"/>
-      <c r="AB36" s="137" t="e">
+      <c r="V36" s="89"/>
+      <c r="W36" s="89"/>
+      <c r="X36" s="89"/>
+      <c r="Y36" s="89"/>
+      <c r="Z36" s="89"/>
+      <c r="AA36" s="89"/>
+      <c r="AB36" s="124" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="AC36" s="137"/>
-      <c r="AD36" s="137"/>
+      <c r="AC36" s="124"/>
+      <c r="AD36" s="124"/>
       <c r="AE36" s="88" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
       <c r="AF36" s="88"/>
       <c r="AG36" s="88"/>
-      <c r="AH36" s="91" t="e">
+      <c r="AH36" s="126" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="AI36" s="91"/>
-      <c r="AJ36" s="91"/>
-      <c r="AK36" s="90"/>
-      <c r="AL36" s="90"/>
-      <c r="AM36" s="90"/>
-      <c r="AN36" s="90"/>
-      <c r="AO36" s="90"/>
-      <c r="AP36" s="90"/>
-      <c r="AQ36" s="90"/>
-      <c r="AR36" s="90"/>
-      <c r="AS36" s="90"/>
-      <c r="AT36" s="90"/>
-      <c r="AU36" s="90"/>
-      <c r="AV36" s="90"/>
+      <c r="AI36" s="126"/>
+      <c r="AJ36" s="126"/>
+      <c r="AK36" s="89"/>
+      <c r="AL36" s="89"/>
+      <c r="AM36" s="89"/>
+      <c r="AN36" s="89"/>
+      <c r="AO36" s="89"/>
+      <c r="AP36" s="89"/>
+      <c r="AQ36" s="89"/>
+      <c r="AR36" s="89"/>
+      <c r="AS36" s="89"/>
+      <c r="AT36" s="89"/>
+      <c r="AU36" s="89"/>
+      <c r="AV36" s="89"/>
       <c r="AW36" s="38"/>
       <c r="AX36" s="18"/>
     </row>
@@ -6503,46 +6503,46 @@
       <c r="T37" s="82">
         <v>7</v>
       </c>
-      <c r="U37" s="103" t="e">
+      <c r="U37" s="176" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="V37" s="103"/>
-      <c r="W37" s="103"/>
-      <c r="X37" s="103"/>
-      <c r="Y37" s="103"/>
-      <c r="Z37" s="103"/>
-      <c r="AA37" s="103"/>
-      <c r="AB37" s="137" t="e">
+      <c r="V37" s="176"/>
+      <c r="W37" s="176"/>
+      <c r="X37" s="176"/>
+      <c r="Y37" s="176"/>
+      <c r="Z37" s="176"/>
+      <c r="AA37" s="176"/>
+      <c r="AB37" s="124" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="AC37" s="137"/>
-      <c r="AD37" s="137"/>
+      <c r="AC37" s="124"/>
+      <c r="AD37" s="124"/>
       <c r="AE37" s="88" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
       <c r="AF37" s="88"/>
       <c r="AG37" s="88"/>
-      <c r="AH37" s="91" t="e">
+      <c r="AH37" s="126" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="AI37" s="91"/>
-      <c r="AJ37" s="91"/>
-      <c r="AK37" s="90"/>
-      <c r="AL37" s="90"/>
-      <c r="AM37" s="90"/>
-      <c r="AN37" s="90"/>
-      <c r="AO37" s="90"/>
-      <c r="AP37" s="90"/>
-      <c r="AQ37" s="90"/>
-      <c r="AR37" s="90"/>
-      <c r="AS37" s="90"/>
-      <c r="AT37" s="90"/>
-      <c r="AU37" s="90"/>
-      <c r="AV37" s="90"/>
+      <c r="AI37" s="126"/>
+      <c r="AJ37" s="126"/>
+      <c r="AK37" s="89"/>
+      <c r="AL37" s="89"/>
+      <c r="AM37" s="89"/>
+      <c r="AN37" s="89"/>
+      <c r="AO37" s="89"/>
+      <c r="AP37" s="89"/>
+      <c r="AQ37" s="89"/>
+      <c r="AR37" s="89"/>
+      <c r="AS37" s="89"/>
+      <c r="AT37" s="89"/>
+      <c r="AU37" s="89"/>
+      <c r="AV37" s="89"/>
       <c r="AW37" s="38"/>
       <c r="AX37" s="18"/>
     </row>
@@ -6600,106 +6600,106 @@
     </row>
     <row r="39" spans="1:50" s="16" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A39" s="31"/>
-      <c r="B39" s="132"/>
-      <c r="C39" s="132"/>
-      <c r="D39" s="132"/>
-      <c r="E39" s="132"/>
-      <c r="F39" s="132"/>
-      <c r="G39" s="132"/>
-      <c r="H39" s="132"/>
-      <c r="I39" s="132"/>
-      <c r="J39" s="132"/>
-      <c r="K39" s="132"/>
-      <c r="L39" s="132"/>
-      <c r="M39" s="132"/>
-      <c r="N39" s="132"/>
-      <c r="O39" s="132"/>
-      <c r="P39" s="132"/>
-      <c r="Q39" s="132"/>
-      <c r="R39" s="132"/>
-      <c r="S39" s="132"/>
-      <c r="T39" s="132"/>
-      <c r="U39" s="132"/>
-      <c r="V39" s="132"/>
-      <c r="W39" s="132"/>
-      <c r="X39" s="132"/>
-      <c r="Y39" s="132"/>
-      <c r="Z39" s="132"/>
-      <c r="AA39" s="132"/>
-      <c r="AB39" s="132"/>
-      <c r="AC39" s="132"/>
-      <c r="AD39" s="132"/>
-      <c r="AE39" s="132"/>
-      <c r="AF39" s="132"/>
-      <c r="AG39" s="132"/>
-      <c r="AH39" s="132"/>
-      <c r="AI39" s="132"/>
-      <c r="AJ39" s="132"/>
-      <c r="AK39" s="132"/>
-      <c r="AL39" s="132"/>
-      <c r="AM39" s="132"/>
-      <c r="AN39" s="132"/>
-      <c r="AO39" s="132"/>
-      <c r="AP39" s="132"/>
-      <c r="AQ39" s="132"/>
-      <c r="AR39" s="132"/>
-      <c r="AS39" s="132"/>
-      <c r="AT39" s="132"/>
-      <c r="AU39" s="132"/>
-      <c r="AV39" s="132"/>
-      <c r="AW39" s="132"/>
+      <c r="B39" s="122"/>
+      <c r="C39" s="122"/>
+      <c r="D39" s="122"/>
+      <c r="E39" s="122"/>
+      <c r="F39" s="122"/>
+      <c r="G39" s="122"/>
+      <c r="H39" s="122"/>
+      <c r="I39" s="122"/>
+      <c r="J39" s="122"/>
+      <c r="K39" s="122"/>
+      <c r="L39" s="122"/>
+      <c r="M39" s="122"/>
+      <c r="N39" s="122"/>
+      <c r="O39" s="122"/>
+      <c r="P39" s="122"/>
+      <c r="Q39" s="122"/>
+      <c r="R39" s="122"/>
+      <c r="S39" s="122"/>
+      <c r="T39" s="122"/>
+      <c r="U39" s="122"/>
+      <c r="V39" s="122"/>
+      <c r="W39" s="122"/>
+      <c r="X39" s="122"/>
+      <c r="Y39" s="122"/>
+      <c r="Z39" s="122"/>
+      <c r="AA39" s="122"/>
+      <c r="AB39" s="122"/>
+      <c r="AC39" s="122"/>
+      <c r="AD39" s="122"/>
+      <c r="AE39" s="122"/>
+      <c r="AF39" s="122"/>
+      <c r="AG39" s="122"/>
+      <c r="AH39" s="122"/>
+      <c r="AI39" s="122"/>
+      <c r="AJ39" s="122"/>
+      <c r="AK39" s="122"/>
+      <c r="AL39" s="122"/>
+      <c r="AM39" s="122"/>
+      <c r="AN39" s="122"/>
+      <c r="AO39" s="122"/>
+      <c r="AP39" s="122"/>
+      <c r="AQ39" s="122"/>
+      <c r="AR39" s="122"/>
+      <c r="AS39" s="122"/>
+      <c r="AT39" s="122"/>
+      <c r="AU39" s="122"/>
+      <c r="AV39" s="122"/>
+      <c r="AW39" s="122"/>
       <c r="AX39" s="18"/>
     </row>
     <row r="40" spans="1:50" s="16" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A40" s="31"/>
-      <c r="B40" s="133"/>
-      <c r="C40" s="133"/>
-      <c r="D40" s="133"/>
-      <c r="E40" s="133"/>
-      <c r="F40" s="133"/>
-      <c r="G40" s="133"/>
-      <c r="H40" s="133"/>
-      <c r="I40" s="133"/>
-      <c r="J40" s="133"/>
-      <c r="K40" s="133"/>
-      <c r="L40" s="133"/>
-      <c r="M40" s="133"/>
-      <c r="N40" s="133"/>
-      <c r="O40" s="133"/>
-      <c r="P40" s="133"/>
-      <c r="Q40" s="133"/>
-      <c r="R40" s="133"/>
-      <c r="S40" s="133"/>
-      <c r="T40" s="133"/>
-      <c r="U40" s="133"/>
-      <c r="V40" s="133"/>
-      <c r="W40" s="133"/>
-      <c r="X40" s="133"/>
-      <c r="Y40" s="133"/>
-      <c r="Z40" s="133"/>
-      <c r="AA40" s="133"/>
-      <c r="AB40" s="133"/>
-      <c r="AC40" s="133"/>
-      <c r="AD40" s="133"/>
-      <c r="AE40" s="133"/>
-      <c r="AF40" s="133"/>
-      <c r="AG40" s="133"/>
-      <c r="AH40" s="133"/>
-      <c r="AI40" s="133"/>
-      <c r="AJ40" s="133"/>
-      <c r="AK40" s="133"/>
-      <c r="AL40" s="133"/>
-      <c r="AM40" s="133"/>
-      <c r="AN40" s="133"/>
-      <c r="AO40" s="133"/>
-      <c r="AP40" s="133"/>
-      <c r="AQ40" s="133"/>
-      <c r="AR40" s="133"/>
-      <c r="AS40" s="133"/>
-      <c r="AT40" s="133"/>
-      <c r="AU40" s="133"/>
-      <c r="AV40" s="133"/>
-      <c r="AW40" s="133"/>
+      <c r="B40" s="123"/>
+      <c r="C40" s="123"/>
+      <c r="D40" s="123"/>
+      <c r="E40" s="123"/>
+      <c r="F40" s="123"/>
+      <c r="G40" s="123"/>
+      <c r="H40" s="123"/>
+      <c r="I40" s="123"/>
+      <c r="J40" s="123"/>
+      <c r="K40" s="123"/>
+      <c r="L40" s="123"/>
+      <c r="M40" s="123"/>
+      <c r="N40" s="123"/>
+      <c r="O40" s="123"/>
+      <c r="P40" s="123"/>
+      <c r="Q40" s="123"/>
+      <c r="R40" s="123"/>
+      <c r="S40" s="123"/>
+      <c r="T40" s="123"/>
+      <c r="U40" s="123"/>
+      <c r="V40" s="123"/>
+      <c r="W40" s="123"/>
+      <c r="X40" s="123"/>
+      <c r="Y40" s="123"/>
+      <c r="Z40" s="123"/>
+      <c r="AA40" s="123"/>
+      <c r="AB40" s="123"/>
+      <c r="AC40" s="123"/>
+      <c r="AD40" s="123"/>
+      <c r="AE40" s="123"/>
+      <c r="AF40" s="123"/>
+      <c r="AG40" s="123"/>
+      <c r="AH40" s="123"/>
+      <c r="AI40" s="123"/>
+      <c r="AJ40" s="123"/>
+      <c r="AK40" s="123"/>
+      <c r="AL40" s="123"/>
+      <c r="AM40" s="123"/>
+      <c r="AN40" s="123"/>
+      <c r="AO40" s="123"/>
+      <c r="AP40" s="123"/>
+      <c r="AQ40" s="123"/>
+      <c r="AR40" s="123"/>
+      <c r="AS40" s="123"/>
+      <c r="AT40" s="123"/>
+      <c r="AU40" s="123"/>
+      <c r="AV40" s="123"/>
+      <c r="AW40" s="123"/>
       <c r="AX40" s="18"/>
     </row>
     <row r="41" spans="1:50" s="16" customFormat="1" ht="20.100000000000001" customHeight="1">
@@ -6755,62 +6755,62 @@
       <c r="AX41" s="46"/>
     </row>
     <row r="42" spans="1:50" s="16" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A42" s="92" t="s">
+      <c r="A42" s="117" t="s">
         <v>21</v>
       </c>
-      <c r="B42" s="93"/>
-      <c r="C42" s="93"/>
-      <c r="D42" s="93"/>
-      <c r="E42" s="93"/>
-      <c r="F42" s="93"/>
-      <c r="G42" s="93"/>
-      <c r="H42" s="93"/>
-      <c r="I42" s="93"/>
-      <c r="J42" s="93"/>
-      <c r="K42" s="93"/>
-      <c r="L42" s="93"/>
-      <c r="M42" s="93"/>
-      <c r="N42" s="93"/>
-      <c r="O42" s="93"/>
-      <c r="P42" s="93"/>
-      <c r="Q42" s="93"/>
-      <c r="R42" s="93" t="s">
+      <c r="B42" s="118"/>
+      <c r="C42" s="118"/>
+      <c r="D42" s="118"/>
+      <c r="E42" s="118"/>
+      <c r="F42" s="118"/>
+      <c r="G42" s="118"/>
+      <c r="H42" s="118"/>
+      <c r="I42" s="118"/>
+      <c r="J42" s="118"/>
+      <c r="K42" s="118"/>
+      <c r="L42" s="118"/>
+      <c r="M42" s="118"/>
+      <c r="N42" s="118"/>
+      <c r="O42" s="118"/>
+      <c r="P42" s="118"/>
+      <c r="Q42" s="118"/>
+      <c r="R42" s="118" t="s">
         <v>22</v>
       </c>
-      <c r="S42" s="93"/>
-      <c r="T42" s="93"/>
-      <c r="U42" s="93"/>
-      <c r="V42" s="93"/>
-      <c r="W42" s="93"/>
-      <c r="X42" s="93"/>
-      <c r="Y42" s="93"/>
-      <c r="Z42" s="93"/>
-      <c r="AA42" s="93"/>
-      <c r="AB42" s="93"/>
-      <c r="AC42" s="93"/>
-      <c r="AD42" s="93"/>
-      <c r="AE42" s="93"/>
-      <c r="AF42" s="93"/>
-      <c r="AG42" s="93"/>
-      <c r="AH42" s="93"/>
-      <c r="AI42" s="94" t="s">
+      <c r="S42" s="118"/>
+      <c r="T42" s="118"/>
+      <c r="U42" s="118"/>
+      <c r="V42" s="118"/>
+      <c r="W42" s="118"/>
+      <c r="X42" s="118"/>
+      <c r="Y42" s="118"/>
+      <c r="Z42" s="118"/>
+      <c r="AA42" s="118"/>
+      <c r="AB42" s="118"/>
+      <c r="AC42" s="118"/>
+      <c r="AD42" s="118"/>
+      <c r="AE42" s="118"/>
+      <c r="AF42" s="118"/>
+      <c r="AG42" s="118"/>
+      <c r="AH42" s="118"/>
+      <c r="AI42" s="119" t="s">
         <v>23</v>
       </c>
-      <c r="AJ42" s="95"/>
-      <c r="AK42" s="95"/>
-      <c r="AL42" s="95"/>
-      <c r="AM42" s="95"/>
-      <c r="AN42" s="95"/>
-      <c r="AO42" s="95"/>
-      <c r="AP42" s="95"/>
-      <c r="AQ42" s="95"/>
-      <c r="AR42" s="95"/>
-      <c r="AS42" s="95"/>
-      <c r="AT42" s="95"/>
-      <c r="AU42" s="95"/>
-      <c r="AV42" s="95"/>
-      <c r="AW42" s="95"/>
-      <c r="AX42" s="96"/>
+      <c r="AJ42" s="120"/>
+      <c r="AK42" s="120"/>
+      <c r="AL42" s="120"/>
+      <c r="AM42" s="120"/>
+      <c r="AN42" s="120"/>
+      <c r="AO42" s="120"/>
+      <c r="AP42" s="120"/>
+      <c r="AQ42" s="120"/>
+      <c r="AR42" s="120"/>
+      <c r="AS42" s="120"/>
+      <c r="AT42" s="120"/>
+      <c r="AU42" s="120"/>
+      <c r="AV42" s="120"/>
+      <c r="AW42" s="120"/>
+      <c r="AX42" s="121"/>
     </row>
     <row r="43" spans="1:50" s="20" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A43" s="52"/>
@@ -6922,17 +6922,17 @@
       <c r="C45" s="56" t="s">
         <v>24</v>
       </c>
-      <c r="D45" s="90"/>
-      <c r="E45" s="90"/>
-      <c r="F45" s="90"/>
-      <c r="G45" s="90"/>
-      <c r="H45" s="90"/>
-      <c r="I45" s="90"/>
-      <c r="J45" s="90"/>
-      <c r="K45" s="90"/>
-      <c r="L45" s="90"/>
-      <c r="M45" s="90"/>
-      <c r="N45" s="90"/>
+      <c r="D45" s="89"/>
+      <c r="E45" s="89"/>
+      <c r="F45" s="89"/>
+      <c r="G45" s="89"/>
+      <c r="H45" s="89"/>
+      <c r="I45" s="89"/>
+      <c r="J45" s="89"/>
+      <c r="K45" s="89"/>
+      <c r="L45" s="89"/>
+      <c r="M45" s="89"/>
+      <c r="N45" s="89"/>
       <c r="O45" t="s">
         <v>25</v>
       </c>
@@ -6943,17 +6943,17 @@
       <c r="T45" s="56" t="s">
         <v>24</v>
       </c>
-      <c r="U45" s="90"/>
-      <c r="V45" s="90"/>
-      <c r="W45" s="90"/>
-      <c r="X45" s="90"/>
-      <c r="Y45" s="90"/>
-      <c r="Z45" s="90"/>
-      <c r="AA45" s="90"/>
-      <c r="AB45" s="90"/>
-      <c r="AC45" s="90"/>
-      <c r="AD45" s="90"/>
-      <c r="AE45" s="90"/>
+      <c r="U45" s="89"/>
+      <c r="V45" s="89"/>
+      <c r="W45" s="89"/>
+      <c r="X45" s="89"/>
+      <c r="Y45" s="89"/>
+      <c r="Z45" s="89"/>
+      <c r="AA45" s="89"/>
+      <c r="AB45" s="89"/>
+      <c r="AC45" s="89"/>
+      <c r="AD45" s="89"/>
+      <c r="AE45" s="89"/>
       <c r="AF45" t="s">
         <v>25</v>
       </c>
@@ -6964,17 +6964,17 @@
       <c r="AK45" s="56" t="s">
         <v>24</v>
       </c>
-      <c r="AL45" s="90"/>
-      <c r="AM45" s="90"/>
-      <c r="AN45" s="90"/>
-      <c r="AO45" s="90"/>
-      <c r="AP45" s="90"/>
-      <c r="AQ45" s="90"/>
-      <c r="AR45" s="90"/>
-      <c r="AS45" s="90"/>
-      <c r="AT45" s="90"/>
-      <c r="AU45" s="90"/>
-      <c r="AV45" s="90"/>
+      <c r="AL45" s="89"/>
+      <c r="AM45" s="89"/>
+      <c r="AN45" s="89"/>
+      <c r="AO45" s="89"/>
+      <c r="AP45" s="89"/>
+      <c r="AQ45" s="89"/>
+      <c r="AR45" s="89"/>
+      <c r="AS45" s="89"/>
+      <c r="AT45" s="89"/>
+      <c r="AU45" s="89"/>
+      <c r="AV45" s="89"/>
       <c r="AW45" t="s">
         <v>25</v>
       </c>
@@ -6984,81 +6984,81 @@
       <c r="A46" s="22"/>
       <c r="B46" s="30"/>
       <c r="C46"/>
-      <c r="D46" s="90" t="s">
+      <c r="D46" s="89" t="s">
         <v>55</v>
       </c>
-      <c r="E46" s="90"/>
-      <c r="F46" s="90"/>
+      <c r="E46" s="89"/>
+      <c r="F46" s="89"/>
       <c r="G46" s="57" t="s">
         <v>26</v>
       </c>
-      <c r="H46" s="90" t="s">
+      <c r="H46" s="89" t="s">
         <v>13</v>
       </c>
-      <c r="I46" s="90"/>
-      <c r="J46" s="90"/>
+      <c r="I46" s="89"/>
+      <c r="J46" s="89"/>
       <c r="K46" s="57" t="s">
         <v>26</v>
       </c>
-      <c r="L46" s="90" t="s">
+      <c r="L46" s="89" t="s">
         <v>56</v>
       </c>
-      <c r="M46" s="90"/>
-      <c r="N46" s="90"/>
+      <c r="M46" s="89"/>
+      <c r="N46" s="89"/>
       <c r="O46"/>
       <c r="P46"/>
       <c r="Q46" s="45"/>
       <c r="R46"/>
       <c r="S46"/>
       <c r="T46"/>
-      <c r="U46" s="90" t="s">
+      <c r="U46" s="89" t="s">
         <v>55</v>
       </c>
-      <c r="V46" s="90"/>
-      <c r="W46" s="90"/>
+      <c r="V46" s="89"/>
+      <c r="W46" s="89"/>
       <c r="X46" s="57" t="s">
         <v>26</v>
       </c>
-      <c r="Y46" s="90" t="s">
+      <c r="Y46" s="89" t="s">
         <v>13</v>
       </c>
-      <c r="Z46" s="90"/>
-      <c r="AA46" s="90"/>
+      <c r="Z46" s="89"/>
+      <c r="AA46" s="89"/>
       <c r="AB46" s="57" t="s">
         <v>26</v>
       </c>
-      <c r="AC46" s="90" t="s">
+      <c r="AC46" s="89" t="s">
         <v>56</v>
       </c>
-      <c r="AD46" s="90"/>
-      <c r="AE46" s="90"/>
+      <c r="AD46" s="89"/>
+      <c r="AE46" s="89"/>
       <c r="AF46"/>
       <c r="AG46"/>
       <c r="AH46" s="45"/>
       <c r="AI46"/>
       <c r="AJ46"/>
       <c r="AK46"/>
-      <c r="AL46" s="90" t="s">
+      <c r="AL46" s="89" t="s">
         <v>55</v>
       </c>
-      <c r="AM46" s="90"/>
-      <c r="AN46" s="90"/>
+      <c r="AM46" s="89"/>
+      <c r="AN46" s="89"/>
       <c r="AO46" s="57" t="s">
         <v>26</v>
       </c>
-      <c r="AP46" s="90" t="s">
+      <c r="AP46" s="89" t="s">
         <v>13</v>
       </c>
-      <c r="AQ46" s="90"/>
-      <c r="AR46" s="90"/>
+      <c r="AQ46" s="89"/>
+      <c r="AR46" s="89"/>
       <c r="AS46" s="57" t="s">
         <v>26</v>
       </c>
-      <c r="AT46" s="90" t="s">
+      <c r="AT46" s="89" t="s">
         <v>56</v>
       </c>
-      <c r="AU46" s="90"/>
-      <c r="AV46" s="90"/>
+      <c r="AU46" s="89"/>
+      <c r="AV46" s="89"/>
       <c r="AW46"/>
       <c r="AX46" s="33"/>
     </row>
@@ -7121,47 +7121,82 @@
   </sheetData>
   <dataConsolidate/>
   <mergeCells count="141">
-    <mergeCell ref="F6:Q6"/>
-    <mergeCell ref="I7:Q7"/>
-    <mergeCell ref="I8:Q8"/>
-    <mergeCell ref="I9:Q9"/>
-    <mergeCell ref="AG9:AI9"/>
-    <mergeCell ref="N1:AH3"/>
-    <mergeCell ref="AP1:AX1"/>
-    <mergeCell ref="AP2:AX2"/>
-    <mergeCell ref="AP3:AX3"/>
-    <mergeCell ref="W7:AA7"/>
-    <mergeCell ref="AB7:AV7"/>
-    <mergeCell ref="V6:AW6"/>
-    <mergeCell ref="AB8:AV8"/>
-    <mergeCell ref="W9:Z9"/>
-    <mergeCell ref="AA9:AB9"/>
-    <mergeCell ref="AD9:AE9"/>
-    <mergeCell ref="B18:J18"/>
-    <mergeCell ref="K18:N18"/>
-    <mergeCell ref="O18:R18"/>
-    <mergeCell ref="I12:Q12"/>
-    <mergeCell ref="I13:Q13"/>
-    <mergeCell ref="I10:Q10"/>
-    <mergeCell ref="I11:Q11"/>
-    <mergeCell ref="W10:AA10"/>
-    <mergeCell ref="AB10:AV10"/>
-    <mergeCell ref="D46:F46"/>
-    <mergeCell ref="H46:J46"/>
-    <mergeCell ref="L46:N46"/>
-    <mergeCell ref="U46:W46"/>
-    <mergeCell ref="Y46:AA46"/>
-    <mergeCell ref="AC46:AE46"/>
-    <mergeCell ref="A42:Q42"/>
-    <mergeCell ref="R42:AH42"/>
-    <mergeCell ref="AI42:AX42"/>
-    <mergeCell ref="C44:O44"/>
-    <mergeCell ref="D45:N45"/>
-    <mergeCell ref="U45:AE45"/>
-    <mergeCell ref="AL45:AV45"/>
-    <mergeCell ref="AL46:AN46"/>
-    <mergeCell ref="AP46:AR46"/>
-    <mergeCell ref="AT46:AV46"/>
+    <mergeCell ref="O33:R33"/>
+    <mergeCell ref="U33:AA33"/>
+    <mergeCell ref="AB33:AD33"/>
+    <mergeCell ref="AE33:AG33"/>
+    <mergeCell ref="AH33:AJ33"/>
+    <mergeCell ref="AK33:AV33"/>
+    <mergeCell ref="AK36:AV36"/>
+    <mergeCell ref="U37:AA37"/>
+    <mergeCell ref="AB37:AD37"/>
+    <mergeCell ref="AE37:AG37"/>
+    <mergeCell ref="AH37:AJ37"/>
+    <mergeCell ref="AK37:AV37"/>
+    <mergeCell ref="AH34:AJ34"/>
+    <mergeCell ref="AK34:AV34"/>
+    <mergeCell ref="U35:AA35"/>
+    <mergeCell ref="AB35:AD35"/>
+    <mergeCell ref="AE35:AG35"/>
+    <mergeCell ref="AH35:AJ35"/>
+    <mergeCell ref="AK35:AV35"/>
+    <mergeCell ref="U34:AA34"/>
+    <mergeCell ref="AE31:AG31"/>
+    <mergeCell ref="AH31:AJ31"/>
+    <mergeCell ref="AK31:AV31"/>
+    <mergeCell ref="B32:E33"/>
+    <mergeCell ref="F32:J32"/>
+    <mergeCell ref="K32:N32"/>
+    <mergeCell ref="O32:R32"/>
+    <mergeCell ref="U32:AA32"/>
+    <mergeCell ref="AB32:AD32"/>
+    <mergeCell ref="AE32:AG32"/>
+    <mergeCell ref="B30:E31"/>
+    <mergeCell ref="F30:J30"/>
+    <mergeCell ref="K30:N30"/>
+    <mergeCell ref="O30:R30"/>
+    <mergeCell ref="T30:AA30"/>
+    <mergeCell ref="AB30:AD30"/>
+    <mergeCell ref="F31:J31"/>
+    <mergeCell ref="K31:N31"/>
+    <mergeCell ref="O31:R31"/>
+    <mergeCell ref="U31:AA31"/>
+    <mergeCell ref="AH32:AJ32"/>
+    <mergeCell ref="AK32:AV32"/>
+    <mergeCell ref="F33:J33"/>
+    <mergeCell ref="K33:N33"/>
+    <mergeCell ref="B28:E29"/>
+    <mergeCell ref="F28:J28"/>
+    <mergeCell ref="K28:N28"/>
+    <mergeCell ref="O28:R28"/>
+    <mergeCell ref="F29:J29"/>
+    <mergeCell ref="K29:N29"/>
+    <mergeCell ref="O29:R29"/>
+    <mergeCell ref="B26:E27"/>
+    <mergeCell ref="F26:J26"/>
+    <mergeCell ref="K26:N26"/>
+    <mergeCell ref="O26:R26"/>
+    <mergeCell ref="F27:J27"/>
+    <mergeCell ref="K27:N27"/>
+    <mergeCell ref="O27:R27"/>
+    <mergeCell ref="O20:R20"/>
+    <mergeCell ref="F21:J21"/>
+    <mergeCell ref="K21:N21"/>
+    <mergeCell ref="O21:R21"/>
+    <mergeCell ref="B24:E25"/>
+    <mergeCell ref="F24:J24"/>
+    <mergeCell ref="K24:N24"/>
+    <mergeCell ref="O24:R24"/>
+    <mergeCell ref="F25:J25"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="O25:R25"/>
+    <mergeCell ref="B22:E23"/>
+    <mergeCell ref="F22:J22"/>
+    <mergeCell ref="K22:N22"/>
+    <mergeCell ref="O22:R22"/>
+    <mergeCell ref="F23:J23"/>
+    <mergeCell ref="K23:N23"/>
+    <mergeCell ref="O23:R23"/>
     <mergeCell ref="B39:AW39"/>
     <mergeCell ref="B40:AW40"/>
     <mergeCell ref="U36:AA36"/>
@@ -7186,82 +7221,47 @@
     <mergeCell ref="B20:E21"/>
     <mergeCell ref="F20:J20"/>
     <mergeCell ref="K20:N20"/>
-    <mergeCell ref="O20:R20"/>
-    <mergeCell ref="F21:J21"/>
-    <mergeCell ref="K21:N21"/>
-    <mergeCell ref="O21:R21"/>
-    <mergeCell ref="B24:E25"/>
-    <mergeCell ref="F24:J24"/>
-    <mergeCell ref="K24:N24"/>
-    <mergeCell ref="O24:R24"/>
-    <mergeCell ref="F25:J25"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="O25:R25"/>
-    <mergeCell ref="B22:E23"/>
-    <mergeCell ref="F22:J22"/>
-    <mergeCell ref="K22:N22"/>
-    <mergeCell ref="O22:R22"/>
-    <mergeCell ref="F23:J23"/>
-    <mergeCell ref="K23:N23"/>
-    <mergeCell ref="O23:R23"/>
-    <mergeCell ref="B28:E29"/>
-    <mergeCell ref="F28:J28"/>
-    <mergeCell ref="K28:N28"/>
-    <mergeCell ref="O28:R28"/>
-    <mergeCell ref="F29:J29"/>
-    <mergeCell ref="K29:N29"/>
-    <mergeCell ref="O29:R29"/>
-    <mergeCell ref="B26:E27"/>
-    <mergeCell ref="F26:J26"/>
-    <mergeCell ref="K26:N26"/>
-    <mergeCell ref="O26:R26"/>
-    <mergeCell ref="F27:J27"/>
-    <mergeCell ref="K27:N27"/>
-    <mergeCell ref="O27:R27"/>
-    <mergeCell ref="AE31:AG31"/>
-    <mergeCell ref="AH31:AJ31"/>
-    <mergeCell ref="AK31:AV31"/>
-    <mergeCell ref="B32:E33"/>
-    <mergeCell ref="F32:J32"/>
-    <mergeCell ref="K32:N32"/>
-    <mergeCell ref="O32:R32"/>
-    <mergeCell ref="U32:AA32"/>
-    <mergeCell ref="AB32:AD32"/>
-    <mergeCell ref="AE32:AG32"/>
-    <mergeCell ref="B30:E31"/>
-    <mergeCell ref="F30:J30"/>
-    <mergeCell ref="K30:N30"/>
-    <mergeCell ref="O30:R30"/>
-    <mergeCell ref="T30:AA30"/>
-    <mergeCell ref="AB30:AD30"/>
-    <mergeCell ref="F31:J31"/>
-    <mergeCell ref="K31:N31"/>
-    <mergeCell ref="O31:R31"/>
-    <mergeCell ref="U31:AA31"/>
-    <mergeCell ref="AH32:AJ32"/>
-    <mergeCell ref="AK32:AV32"/>
-    <mergeCell ref="F33:J33"/>
-    <mergeCell ref="K33:N33"/>
-    <mergeCell ref="O33:R33"/>
-    <mergeCell ref="U33:AA33"/>
-    <mergeCell ref="AB33:AD33"/>
-    <mergeCell ref="AE33:AG33"/>
-    <mergeCell ref="AH33:AJ33"/>
-    <mergeCell ref="AK33:AV33"/>
-    <mergeCell ref="AK36:AV36"/>
-    <mergeCell ref="U37:AA37"/>
-    <mergeCell ref="AB37:AD37"/>
-    <mergeCell ref="AE37:AG37"/>
-    <mergeCell ref="AH37:AJ37"/>
-    <mergeCell ref="AK37:AV37"/>
-    <mergeCell ref="AH34:AJ34"/>
-    <mergeCell ref="AK34:AV34"/>
-    <mergeCell ref="U35:AA35"/>
-    <mergeCell ref="AB35:AD35"/>
-    <mergeCell ref="AE35:AG35"/>
-    <mergeCell ref="AH35:AJ35"/>
-    <mergeCell ref="AK35:AV35"/>
-    <mergeCell ref="U34:AA34"/>
+    <mergeCell ref="D46:F46"/>
+    <mergeCell ref="H46:J46"/>
+    <mergeCell ref="L46:N46"/>
+    <mergeCell ref="U46:W46"/>
+    <mergeCell ref="Y46:AA46"/>
+    <mergeCell ref="AC46:AE46"/>
+    <mergeCell ref="A42:Q42"/>
+    <mergeCell ref="R42:AH42"/>
+    <mergeCell ref="AI42:AX42"/>
+    <mergeCell ref="C44:O44"/>
+    <mergeCell ref="D45:N45"/>
+    <mergeCell ref="U45:AE45"/>
+    <mergeCell ref="AL45:AV45"/>
+    <mergeCell ref="AL46:AN46"/>
+    <mergeCell ref="AP46:AR46"/>
+    <mergeCell ref="AT46:AV46"/>
+    <mergeCell ref="B18:J18"/>
+    <mergeCell ref="K18:N18"/>
+    <mergeCell ref="O18:R18"/>
+    <mergeCell ref="I12:Q12"/>
+    <mergeCell ref="I13:Q13"/>
+    <mergeCell ref="I10:Q10"/>
+    <mergeCell ref="I11:Q11"/>
+    <mergeCell ref="W10:AA10"/>
+    <mergeCell ref="AB10:AV10"/>
+    <mergeCell ref="F6:Q6"/>
+    <mergeCell ref="I7:Q7"/>
+    <mergeCell ref="I8:Q8"/>
+    <mergeCell ref="I9:Q9"/>
+    <mergeCell ref="AG9:AI9"/>
+    <mergeCell ref="N1:AH3"/>
+    <mergeCell ref="AP1:AX1"/>
+    <mergeCell ref="AP2:AX2"/>
+    <mergeCell ref="AP3:AX3"/>
+    <mergeCell ref="W7:AA7"/>
+    <mergeCell ref="AB7:AV7"/>
+    <mergeCell ref="V6:AW6"/>
+    <mergeCell ref="AB8:AV8"/>
+    <mergeCell ref="W9:Z9"/>
+    <mergeCell ref="AA9:AB9"/>
+    <mergeCell ref="AD9:AE9"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0.19" top="0" bottom="0" header="0" footer="0"/>
@@ -7391,16 +7391,8 @@
       </c>
     </row>
     <row r="2" spans="1:21">
-      <c r="A2" s="30">
-        <v>0</v>
-      </c>
-      <c r="I2" s="30" t="s">
-        <v>33</v>
-      </c>
+      <c r="A2" s="30"/>
       <c r="L2" s="30"/>
-      <c r="T2" s="30" t="s">
-        <v>4</v>
-      </c>
     </row>
     <row r="3" spans="1:21">
       <c r="A3" s="30">
@@ -7428,7 +7420,7 @@
         <v>78</v>
       </c>
       <c r="I3" s="30" t="s">
-        <v>79</v>
+        <v>33</v>
       </c>
       <c r="J3" s="30" t="s">
         <v>80</v>
@@ -7458,7 +7450,7 @@
         <v>52</v>
       </c>
       <c r="T3" s="30" t="s">
-        <v>84</v>
+        <v>4</v>
       </c>
       <c r="U3" s="30" t="s">
         <v>85</v>
@@ -7489,6 +7481,9 @@
       <c r="H4" s="30" t="s">
         <v>90</v>
       </c>
+      <c r="I4" s="30" t="s">
+        <v>79</v>
+      </c>
       <c r="J4" s="30" t="s">
         <v>17</v>
       </c>
@@ -7516,6 +7511,9 @@
       </c>
       <c r="R4" s="30" t="s">
         <v>53</v>
+      </c>
+      <c r="T4" s="30" t="s">
+        <v>84</v>
       </c>
       <c r="U4" s="87" t="s">
         <v>94</v>
@@ -8082,13 +8080,13 @@
       <c r="B3" s="177"/>
       <c r="C3" s="177"/>
       <c r="D3" s="177"/>
-      <c r="E3" s="137" t="s">
+      <c r="E3" s="124" t="s">
         <v>175</v>
       </c>
-      <c r="F3" s="137"/>
-      <c r="G3" s="137"/>
-      <c r="H3" s="137"/>
-      <c r="I3" s="137"/>
+      <c r="F3" s="124"/>
+      <c r="G3" s="124"/>
+      <c r="H3" s="124"/>
+      <c r="I3" s="124"/>
       <c r="J3" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -8110,13 +8108,13 @@
       <c r="B4" s="177"/>
       <c r="C4" s="177"/>
       <c r="D4" s="177"/>
-      <c r="E4" s="137" t="s">
+      <c r="E4" s="124" t="s">
         <v>46</v>
       </c>
-      <c r="F4" s="137"/>
-      <c r="G4" s="137"/>
-      <c r="H4" s="137"/>
-      <c r="I4" s="137"/>
+      <c r="F4" s="124"/>
+      <c r="G4" s="124"/>
+      <c r="H4" s="124"/>
+      <c r="I4" s="124"/>
       <c r="J4" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -8140,13 +8138,13 @@
       <c r="B5" s="177"/>
       <c r="C5" s="177"/>
       <c r="D5" s="177"/>
-      <c r="E5" s="137" t="s">
+      <c r="E5" s="124" t="s">
         <v>175</v>
       </c>
-      <c r="F5" s="137"/>
-      <c r="G5" s="137"/>
-      <c r="H5" s="137"/>
-      <c r="I5" s="137"/>
+      <c r="F5" s="124"/>
+      <c r="G5" s="124"/>
+      <c r="H5" s="124"/>
+      <c r="I5" s="124"/>
       <c r="J5" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -8168,13 +8166,13 @@
       <c r="B6" s="177"/>
       <c r="C6" s="177"/>
       <c r="D6" s="177"/>
-      <c r="E6" s="137" t="s">
+      <c r="E6" s="124" t="s">
         <v>46</v>
       </c>
-      <c r="F6" s="137"/>
-      <c r="G6" s="137"/>
-      <c r="H6" s="137"/>
-      <c r="I6" s="137"/>
+      <c r="F6" s="124"/>
+      <c r="G6" s="124"/>
+      <c r="H6" s="124"/>
+      <c r="I6" s="124"/>
       <c r="J6" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -8198,13 +8196,13 @@
       <c r="B7" s="177"/>
       <c r="C7" s="177"/>
       <c r="D7" s="177"/>
-      <c r="E7" s="137" t="s">
+      <c r="E7" s="124" t="s">
         <v>175</v>
       </c>
-      <c r="F7" s="137"/>
-      <c r="G7" s="137"/>
-      <c r="H7" s="137"/>
-      <c r="I7" s="137"/>
+      <c r="F7" s="124"/>
+      <c r="G7" s="124"/>
+      <c r="H7" s="124"/>
+      <c r="I7" s="124"/>
       <c r="J7" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -8226,13 +8224,13 @@
       <c r="B8" s="177"/>
       <c r="C8" s="177"/>
       <c r="D8" s="177"/>
-      <c r="E8" s="137" t="s">
+      <c r="E8" s="124" t="s">
         <v>46</v>
       </c>
-      <c r="F8" s="137"/>
-      <c r="G8" s="137"/>
-      <c r="H8" s="137"/>
-      <c r="I8" s="137"/>
+      <c r="F8" s="124"/>
+      <c r="G8" s="124"/>
+      <c r="H8" s="124"/>
+      <c r="I8" s="124"/>
       <c r="J8" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -8256,13 +8254,13 @@
       <c r="B9" s="177"/>
       <c r="C9" s="177"/>
       <c r="D9" s="177"/>
-      <c r="E9" s="137" t="s">
+      <c r="E9" s="124" t="s">
         <v>175</v>
       </c>
-      <c r="F9" s="137"/>
-      <c r="G9" s="137"/>
-      <c r="H9" s="137"/>
-      <c r="I9" s="137"/>
+      <c r="F9" s="124"/>
+      <c r="G9" s="124"/>
+      <c r="H9" s="124"/>
+      <c r="I9" s="124"/>
       <c r="J9" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -8284,13 +8282,13 @@
       <c r="B10" s="177"/>
       <c r="C10" s="177"/>
       <c r="D10" s="177"/>
-      <c r="E10" s="137" t="s">
+      <c r="E10" s="124" t="s">
         <v>46</v>
       </c>
-      <c r="F10" s="137"/>
-      <c r="G10" s="137"/>
-      <c r="H10" s="137"/>
-      <c r="I10" s="137"/>
+      <c r="F10" s="124"/>
+      <c r="G10" s="124"/>
+      <c r="H10" s="124"/>
+      <c r="I10" s="124"/>
       <c r="J10" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -8311,13 +8309,13 @@
       <c r="B11" s="177"/>
       <c r="C11" s="177"/>
       <c r="D11" s="177"/>
-      <c r="E11" s="137" t="s">
+      <c r="E11" s="124" t="s">
         <v>175</v>
       </c>
-      <c r="F11" s="137"/>
-      <c r="G11" s="137"/>
-      <c r="H11" s="137"/>
-      <c r="I11" s="137"/>
+      <c r="F11" s="124"/>
+      <c r="G11" s="124"/>
+      <c r="H11" s="124"/>
+      <c r="I11" s="124"/>
       <c r="J11" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -8336,13 +8334,13 @@
       <c r="B12" s="177"/>
       <c r="C12" s="177"/>
       <c r="D12" s="177"/>
-      <c r="E12" s="137" t="s">
+      <c r="E12" s="124" t="s">
         <v>46</v>
       </c>
-      <c r="F12" s="137"/>
-      <c r="G12" s="137"/>
-      <c r="H12" s="137"/>
-      <c r="I12" s="137"/>
+      <c r="F12" s="124"/>
+      <c r="G12" s="124"/>
+      <c r="H12" s="124"/>
+      <c r="I12" s="124"/>
       <c r="J12" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -8363,13 +8361,13 @@
       <c r="B13" s="177"/>
       <c r="C13" s="177"/>
       <c r="D13" s="177"/>
-      <c r="E13" s="137" t="s">
+      <c r="E13" s="124" t="s">
         <v>175</v>
       </c>
-      <c r="F13" s="137"/>
-      <c r="G13" s="137"/>
-      <c r="H13" s="137"/>
-      <c r="I13" s="137"/>
+      <c r="F13" s="124"/>
+      <c r="G13" s="124"/>
+      <c r="H13" s="124"/>
+      <c r="I13" s="124"/>
       <c r="J13" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -8388,13 +8386,13 @@
       <c r="B14" s="177"/>
       <c r="C14" s="177"/>
       <c r="D14" s="177"/>
-      <c r="E14" s="137" t="s">
+      <c r="E14" s="124" t="s">
         <v>46</v>
       </c>
-      <c r="F14" s="137"/>
-      <c r="G14" s="137"/>
-      <c r="H14" s="137"/>
-      <c r="I14" s="137"/>
+      <c r="F14" s="124"/>
+      <c r="G14" s="124"/>
+      <c r="H14" s="124"/>
+      <c r="I14" s="124"/>
       <c r="J14" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -8415,13 +8413,13 @@
       <c r="B15" s="177"/>
       <c r="C15" s="177"/>
       <c r="D15" s="177"/>
-      <c r="E15" s="137" t="s">
+      <c r="E15" s="124" t="s">
         <v>175</v>
       </c>
-      <c r="F15" s="137"/>
-      <c r="G15" s="137"/>
-      <c r="H15" s="137"/>
-      <c r="I15" s="137"/>
+      <c r="F15" s="124"/>
+      <c r="G15" s="124"/>
+      <c r="H15" s="124"/>
+      <c r="I15" s="124"/>
       <c r="J15" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -8440,13 +8438,13 @@
       <c r="B16" s="177"/>
       <c r="C16" s="177"/>
       <c r="D16" s="177"/>
-      <c r="E16" s="137" t="s">
+      <c r="E16" s="124" t="s">
         <v>46</v>
       </c>
-      <c r="F16" s="137"/>
-      <c r="G16" s="137"/>
-      <c r="H16" s="137"/>
-      <c r="I16" s="137"/>
+      <c r="F16" s="124"/>
+      <c r="G16" s="124"/>
+      <c r="H16" s="124"/>
+      <c r="I16" s="124"/>
       <c r="J16" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -8462,20 +8460,6 @@
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="A5:D6"/>
-    <mergeCell ref="E5:I5"/>
-    <mergeCell ref="E6:I6"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A3:D4"/>
-    <mergeCell ref="E3:I3"/>
-    <mergeCell ref="E4:I4"/>
-    <mergeCell ref="A7:D8"/>
-    <mergeCell ref="E7:I7"/>
-    <mergeCell ref="E8:I8"/>
-    <mergeCell ref="A9:D10"/>
-    <mergeCell ref="E9:I9"/>
-    <mergeCell ref="E10:I10"/>
     <mergeCell ref="A15:D16"/>
     <mergeCell ref="E15:I15"/>
     <mergeCell ref="E16:I16"/>
@@ -8485,6 +8469,20 @@
     <mergeCell ref="A13:D14"/>
     <mergeCell ref="E13:I13"/>
     <mergeCell ref="E14:I14"/>
+    <mergeCell ref="A7:D8"/>
+    <mergeCell ref="E7:I7"/>
+    <mergeCell ref="E8:I8"/>
+    <mergeCell ref="A9:D10"/>
+    <mergeCell ref="E9:I9"/>
+    <mergeCell ref="E10:I10"/>
+    <mergeCell ref="A5:D6"/>
+    <mergeCell ref="E5:I5"/>
+    <mergeCell ref="E6:I6"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A3:D4"/>
+    <mergeCell ref="E3:I3"/>
+    <mergeCell ref="E4:I4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
@@ -8503,21 +8501,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b3bbc11e-4fb5-4621-843c-15cf5fb29021">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="bf49118c-070b-4d5d-8853-086408e6e32f" xsi:nil="true"/>
-    <Wiphaphon_x002e_kh xmlns="b3bbc11e-4fb5-4621-843c-15cf5fb29021">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Wiphaphon_x002e_kh>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8802,12 +8791,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b3bbc11e-4fb5-4621-843c-15cf5fb29021">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="bf49118c-070b-4d5d-8853-086408e6e32f" xsi:nil="true"/>
+    <Wiphaphon_x002e_kh xmlns="b3bbc11e-4fb5-4621-843c-15cf5fb29021">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Wiphaphon_x002e_kh>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8815,12 +8813,9 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{786D557F-2E62-4128-9B9B-39D75D14CA48}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{356DB7B6-6350-4A86-BC8B-65ECD8CBAF45}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="b3bbc11e-4fb5-4621-843c-15cf5fb29021"/>
-    <ds:schemaRef ds:uri="bf49118c-070b-4d5d-8853-086408e6e32f"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -8845,9 +8840,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{356DB7B6-6350-4A86-BC8B-65ECD8CBAF45}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{786D557F-2E62-4128-9B9B-39D75D14CA48}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="b3bbc11e-4fb5-4621-843c-15cf5fb29021"/>
+    <ds:schemaRef ds:uri="bf49118c-070b-4d5d-8853-086408e6e32f"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
